--- a/output/xlsx/eoss-398.xlsx
+++ b/output/xlsx/eoss-398.xlsx
@@ -3636,7 +3636,7 @@
         <v>46144.29255796297</v>
       </c>
       <c r="D2" s="1">
-        <v>46144.54253472222</v>
+        <v>46144.29253472222</v>
       </c>
       <c r="E2">
         <v>5222</v>
@@ -3743,7 +3743,7 @@
         <v>46144.292735219904</v>
       </c>
       <c r="D3" s="1">
-        <v>46144.542708333334</v>
+        <v>46144.292708333334</v>
       </c>
       <c r="E3">
         <v>5424</v>
@@ -3853,7 +3853,7 @@
         <v>46144.29290261574</v>
       </c>
       <c r="D4" s="1">
-        <v>46144.54288194444</v>
+        <v>46144.29288194444</v>
       </c>
       <c r="E4">
         <v>5797</v>
@@ -3996,7 +3996,7 @@
         <v>46144.29308858796</v>
       </c>
       <c r="D5" s="1">
-        <v>46144.54305555556</v>
+        <v>46144.29305555556</v>
       </c>
       <c r="E5">
         <v>6051</v>
@@ -4118,7 +4118,7 @@
         <v>46144.29324915509</v>
       </c>
       <c r="D6" s="1">
-        <v>46144.543229166666</v>
+        <v>46144.293229166666</v>
       </c>
       <c r="E6">
         <v>6452</v>
@@ -4261,7 +4261,7 @@
         <v>46144.29343021991</v>
       </c>
       <c r="D7" s="1">
-        <v>46144.54340277778</v>
+        <v>46144.29340277778</v>
       </c>
       <c r="E7">
         <v>6727</v>
@@ -4383,7 +4383,7 @@
         <v>46144.29359678241</v>
       </c>
       <c r="D8" s="1">
-        <v>46144.54357638889</v>
+        <v>46144.29357638889</v>
       </c>
       <c r="E8">
         <v>7170</v>
@@ -4526,7 +4526,7 @@
         <v>46144.2937781713</v>
       </c>
       <c r="D9" s="1">
-        <v>46144.54375</v>
+        <v>46144.29375</v>
       </c>
       <c r="E9">
         <v>7422</v>
@@ -4648,7 +4648,7 @@
         <v>46144.2939440625</v>
       </c>
       <c r="D10" s="1">
-        <v>46144.54392361111</v>
+        <v>46144.29392361111</v>
       </c>
       <c r="E10">
         <v>7827</v>
@@ -4791,7 +4791,7 @@
         <v>46144.29412755787</v>
       </c>
       <c r="D11" s="1">
-        <v>46144.54409722222</v>
+        <v>46144.29409722222</v>
       </c>
       <c r="E11">
         <v>8046</v>
@@ -4913,7 +4913,7 @@
         <v>46144.294291226855</v>
       </c>
       <c r="D12" s="1">
-        <v>46144.544270833336</v>
+        <v>46144.294270833336</v>
       </c>
       <c r="E12">
         <v>8461</v>
@@ -5056,7 +5056,7 @@
         <v>46144.29447184028</v>
       </c>
       <c r="D13" s="1">
-        <v>46144.544444444444</v>
+        <v>46144.294444444444</v>
       </c>
       <c r="E13">
         <v>8738</v>
@@ -5178,7 +5178,7 @@
         <v>46144.29481861111</v>
       </c>
       <c r="D14" s="1">
-        <v>46144.54479166667</v>
+        <v>46144.29479166667</v>
       </c>
       <c r="E14">
         <v>9404</v>
@@ -5300,7 +5300,7 @@
         <v>46144.29516997685</v>
       </c>
       <c r="D15" s="1">
-        <v>46144.54513888889</v>
+        <v>46144.29513888889</v>
       </c>
       <c r="E15">
         <v>10064</v>
@@ -5422,7 +5422,7 @@
         <v>46144.29533332176</v>
       </c>
       <c r="D16" s="1">
-        <v>46144.5453125</v>
+        <v>46144.2953125</v>
       </c>
       <c r="E16">
         <v>10455</v>
@@ -5565,7 +5565,7 @@
         <v>46144.295513460645</v>
       </c>
       <c r="D17" s="1">
-        <v>46144.545486111114</v>
+        <v>46144.295486111114</v>
       </c>
       <c r="E17">
         <v>10700</v>
@@ -5687,7 +5687,7 @@
         <v>46144.295679814815</v>
       </c>
       <c r="D18" s="1">
-        <v>46144.54565972222</v>
+        <v>46144.29565972222</v>
       </c>
       <c r="E18">
         <v>11115</v>
@@ -5830,7 +5830,7 @@
         <v>46144.295860590275</v>
       </c>
       <c r="D19" s="1">
-        <v>46144.54583333333</v>
+        <v>46144.29583333333</v>
       </c>
       <c r="E19">
         <v>11379</v>
@@ -5952,7 +5952,7 @@
         <v>46144.29602782407</v>
       </c>
       <c r="D20" s="1">
-        <v>46144.546006944445</v>
+        <v>46144.296006944445</v>
       </c>
       <c r="E20">
         <v>11806</v>
@@ -6095,7 +6095,7 @@
         <v>46144.296210925924</v>
       </c>
       <c r="D21" s="1">
-        <v>46144.54618055555</v>
+        <v>46144.29618055555</v>
       </c>
       <c r="E21">
         <v>12075</v>
@@ -6217,7 +6217,7 @@
         <v>46144.296555277775</v>
       </c>
       <c r="D22" s="1">
-        <v>46144.54652777778</v>
+        <v>46144.29652777778</v>
       </c>
       <c r="E22">
         <v>12771</v>
@@ -6339,7 +6339,7 @@
         <v>46144.29690197916</v>
       </c>
       <c r="D23" s="1">
-        <v>46144.546875</v>
+        <v>46144.296875</v>
       </c>
       <c r="E23">
         <v>13437</v>
@@ -6461,7 +6461,7 @@
         <v>46144.29725321759</v>
       </c>
       <c r="D24" s="1">
-        <v>46144.54722222222</v>
+        <v>46144.29722222222</v>
       </c>
       <c r="E24">
         <v>14159</v>
@@ -6583,7 +6583,7 @@
         <v>46144.2974159838</v>
       </c>
       <c r="D25" s="1">
-        <v>46144.54739583333</v>
+        <v>46144.29739583333</v>
       </c>
       <c r="E25">
         <v>14611</v>
@@ -6726,7 +6726,7 @@
         <v>46144.29759744213</v>
       </c>
       <c r="D26" s="1">
-        <v>46144.54756944445</v>
+        <v>46144.29756944445</v>
       </c>
       <c r="E26">
         <v>14880</v>
@@ -6848,7 +6848,7 @@
         <v>46144.29776641203</v>
       </c>
       <c r="D27" s="1">
-        <v>46144.547743055555</v>
+        <v>46144.297743055555</v>
       </c>
       <c r="E27">
         <v>15318</v>
@@ -6991,7 +6991,7 @@
         <v>46144.29794386574</v>
       </c>
       <c r="D28" s="1">
-        <v>46144.54791666667</v>
+        <v>46144.29791666667</v>
       </c>
       <c r="E28">
         <v>15550</v>
@@ -7113,7 +7113,7 @@
         <v>46144.29829517361</v>
       </c>
       <c r="D29" s="1">
-        <v>46144.548263888886</v>
+        <v>46144.298263888886</v>
       </c>
       <c r="E29">
         <v>16203</v>
@@ -7235,7 +7235,7 @@
         <v>46144.29863884259</v>
       </c>
       <c r="D30" s="1">
-        <v>46144.54861111111</v>
+        <v>46144.29861111111</v>
       </c>
       <c r="E30">
         <v>16908</v>
@@ -7357,7 +7357,7 @@
         <v>46144.298804907405</v>
       </c>
       <c r="D31" s="1">
-        <v>46144.548784722225</v>
+        <v>46144.298784722225</v>
       </c>
       <c r="E31">
         <v>17365</v>
@@ -7500,7 +7500,7 @@
         <v>46144.298985347225</v>
       </c>
       <c r="D32" s="1">
-        <v>46144.54895833333</v>
+        <v>46144.29895833333</v>
       </c>
       <c r="E32">
         <v>17607</v>
@@ -7622,7 +7622,7 @@
         <v>46144.299152141204</v>
       </c>
       <c r="D33" s="1">
-        <v>46144.54913194444</v>
+        <v>46144.29913194444</v>
       </c>
       <c r="E33">
         <v>18074</v>
@@ -7765,7 +7765,7 @@
         <v>46144.29933692129</v>
       </c>
       <c r="D34" s="1">
-        <v>46144.549305555556</v>
+        <v>46144.299305555556</v>
       </c>
       <c r="E34">
         <v>18323</v>
@@ -7887,7 +7887,7 @@
         <v>46144.299502118054</v>
       </c>
       <c r="D35" s="1">
-        <v>46144.549479166664</v>
+        <v>46144.299479166664</v>
       </c>
       <c r="E35">
         <v>18746</v>
@@ -8030,7 +8030,7 @@
         <v>46144.29967922454</v>
       </c>
       <c r="D36" s="1">
-        <v>46144.54965277778</v>
+        <v>46144.29965277778</v>
       </c>
       <c r="E36">
         <v>19025</v>
@@ -8152,7 +8152,7 @@
         <v>46144.29984693287</v>
       </c>
       <c r="D37" s="1">
-        <v>46144.54982638889</v>
+        <v>46144.29982638889</v>
       </c>
       <c r="E37">
         <v>19450</v>
@@ -8295,7 +8295,7 @@
         <v>46144.300027094905</v>
       </c>
       <c r="D38" s="1">
-        <v>46144.55</v>
+        <v>46144.3</v>
       </c>
       <c r="E38">
         <v>19704</v>
@@ -8417,7 +8417,7 @@
         <v>46144.300194166666</v>
       </c>
       <c r="D39" s="1">
-        <v>46144.55017361111</v>
+        <v>46144.30017361111</v>
       </c>
       <c r="E39">
         <v>20162</v>
@@ -8560,7 +8560,7 @@
         <v>46144.300377997686</v>
       </c>
       <c r="D40" s="1">
-        <v>46144.55034722222</v>
+        <v>46144.30034722222</v>
       </c>
       <c r="E40">
         <v>20432</v>
@@ -8682,7 +8682,7 @@
         <v>46144.30054096065</v>
       </c>
       <c r="D41" s="1">
-        <v>46144.550520833334</v>
+        <v>46144.300520833334</v>
       </c>
       <c r="E41">
         <v>20871</v>
@@ -8825,7 +8825,7 @@
         <v>46144.30072207176</v>
       </c>
       <c r="D42" s="1">
-        <v>46144.55069444444</v>
+        <v>46144.30069444444</v>
       </c>
       <c r="E42">
         <v>21135</v>
@@ -8947,7 +8947,7 @@
         <v>46144.300888275466</v>
       </c>
       <c r="D43" s="1">
-        <v>46144.55086805556</v>
+        <v>46144.30086805556</v>
       </c>
       <c r="E43">
         <v>21575</v>
@@ -9090,7 +9090,7 @@
         <v>46144.301069050925</v>
       </c>
       <c r="D44" s="1">
-        <v>46144.551041666666</v>
+        <v>46144.301041666666</v>
       </c>
       <c r="E44">
         <v>21860</v>
@@ -9212,7 +9212,7 @@
         <v>46144.30123585648</v>
       </c>
       <c r="D45" s="1">
-        <v>46144.55121527778</v>
+        <v>46144.30121527778</v>
       </c>
       <c r="E45">
         <v>22322</v>
@@ -9355,7 +9355,7 @@
         <v>46144.30141934028</v>
       </c>
       <c r="D46" s="1">
-        <v>46144.55138888889</v>
+        <v>46144.30138888889</v>
       </c>
       <c r="E46">
         <v>22598</v>
@@ -9477,7 +9477,7 @@
         <v>46144.301582719905</v>
       </c>
       <c r="D47" s="1">
-        <v>46144.5515625</v>
+        <v>46144.3015625</v>
       </c>
       <c r="E47">
         <v>23073</v>
@@ -9620,7 +9620,7 @@
         <v>46144.301763842595</v>
       </c>
       <c r="D48" s="1">
-        <v>46144.55173611111</v>
+        <v>46144.30173611111</v>
       </c>
       <c r="E48">
         <v>23336</v>
@@ -9742,7 +9742,7 @@
         <v>46144.301929699075</v>
       </c>
       <c r="D49" s="1">
-        <v>46144.55190972222</v>
+        <v>46144.30190972222</v>
       </c>
       <c r="E49">
         <v>23778</v>
@@ -9885,7 +9885,7 @@
         <v>46144.30211127315</v>
       </c>
       <c r="D50" s="1">
-        <v>46144.552083333336</v>
+        <v>46144.302083333336</v>
       </c>
       <c r="E50">
         <v>24065</v>
@@ -10007,7 +10007,7 @@
         <v>46144.3022765625</v>
       </c>
       <c r="D51" s="1">
-        <v>46144.552256944444</v>
+        <v>46144.302256944444</v>
       </c>
       <c r="E51">
         <v>24522</v>
@@ -10150,7 +10150,7 @@
         <v>46144.30246170139</v>
       </c>
       <c r="D52" s="1">
-        <v>46144.55243055556</v>
+        <v>46144.30243055556</v>
       </c>
       <c r="E52">
         <v>24793</v>
@@ -10272,7 +10272,7 @@
         <v>46144.30262440972</v>
       </c>
       <c r="D53" s="1">
-        <v>46144.55260416667</v>
+        <v>46144.30260416667</v>
       </c>
       <c r="E53">
         <v>25244</v>
@@ -10415,7 +10415,7 @@
         <v>46144.30280533565</v>
       </c>
       <c r="D54" s="1">
-        <v>46144.552777777775</v>
+        <v>46144.302777777775</v>
       </c>
       <c r="E54">
         <v>25554</v>
@@ -10537,7 +10537,7 @@
         <v>46144.30297199074</v>
       </c>
       <c r="D55" s="1">
-        <v>46144.55295138889</v>
+        <v>46144.30295138889</v>
       </c>
       <c r="E55">
         <v>26032</v>
@@ -10680,7 +10680,7 @@
         <v>46144.30315262731</v>
       </c>
       <c r="D56" s="1">
-        <v>46144.553125</v>
+        <v>46144.303125</v>
       </c>
       <c r="E56">
         <v>26309</v>
@@ -10802,7 +10802,7 @@
         <v>46144.30331934028</v>
       </c>
       <c r="D57" s="1">
-        <v>46144.553298611114</v>
+        <v>46144.303298611114</v>
       </c>
       <c r="E57">
         <v>26755</v>
@@ -10945,7 +10945,7 @@
         <v>46144.30350340278</v>
       </c>
       <c r="D58" s="1">
-        <v>46144.55347222222</v>
+        <v>46144.30347222222</v>
       </c>
       <c r="E58">
         <v>27047</v>
@@ -11067,7 +11067,7 @@
         <v>46144.30366578704</v>
       </c>
       <c r="D59" s="1">
-        <v>46144.55364583333</v>
+        <v>46144.30364583333</v>
       </c>
       <c r="E59">
         <v>27476</v>
@@ -11210,7 +11210,7 @@
         <v>46144.30384644676</v>
       </c>
       <c r="D60" s="1">
-        <v>46144.553819444445</v>
+        <v>46144.303819444445</v>
       </c>
       <c r="E60">
         <v>27809</v>
@@ -11332,7 +11332,7 @@
         <v>46144.30401313657</v>
       </c>
       <c r="D61" s="1">
-        <v>46144.55399305555</v>
+        <v>46144.30399305555</v>
       </c>
       <c r="E61">
         <v>28279</v>
@@ -11475,7 +11475,7 @@
         <v>46144.30419390046</v>
       </c>
       <c r="D62" s="1">
-        <v>46144.55416666667</v>
+        <v>46144.30416666667</v>
       </c>
       <c r="E62">
         <v>28590</v>
@@ -11597,7 +11597,7 @@
         <v>46144.30436055556</v>
       </c>
       <c r="D63" s="1">
-        <v>46144.55434027778</v>
+        <v>46144.30434027778</v>
       </c>
       <c r="E63">
         <v>29059</v>
@@ -11740,7 +11740,7 @@
         <v>46144.30454489584</v>
       </c>
       <c r="D64" s="1">
-        <v>46144.55451388889</v>
+        <v>46144.30451388889</v>
       </c>
       <c r="E64">
         <v>29351</v>
@@ -11862,7 +11862,7 @@
         <v>46144.30470744213</v>
       </c>
       <c r="D65" s="1">
-        <v>46144.5546875</v>
+        <v>46144.3046875</v>
       </c>
       <c r="E65">
         <v>29867</v>
@@ -12005,7 +12005,7 @@
         <v>46144.304888391205</v>
       </c>
       <c r="D66" s="1">
-        <v>46144.55486111111</v>
+        <v>46144.30486111111</v>
       </c>
       <c r="E66">
         <v>30181</v>
@@ -12127,7 +12127,7 @@
         <v>46144.30505539352</v>
       </c>
       <c r="D67" s="1">
-        <v>46144.55503472222</v>
+        <v>46144.30503472222</v>
       </c>
       <c r="E67">
         <v>30623</v>
@@ -12270,7 +12270,7 @@
         <v>46144.30523574074</v>
       </c>
       <c r="D68" s="1">
-        <v>46144.55520833333</v>
+        <v>46144.30520833333</v>
       </c>
       <c r="E68">
         <v>30952</v>
@@ -12392,7 +12392,7 @@
         <v>46144.30540261574</v>
       </c>
       <c r="D69" s="1">
-        <v>46144.55538194445</v>
+        <v>46144.30538194445</v>
       </c>
       <c r="E69">
         <v>31431</v>
@@ -12535,7 +12535,7 @@
         <v>46144.30558607639</v>
       </c>
       <c r="D70" s="1">
-        <v>46144.555555555555</v>
+        <v>46144.305555555555</v>
       </c>
       <c r="E70">
         <v>31736</v>
@@ -12657,7 +12657,7 @@
         <v>46144.30574895833</v>
       </c>
       <c r="D71" s="1">
-        <v>46144.55572916667</v>
+        <v>46144.30572916667</v>
       </c>
       <c r="E71">
         <v>32157</v>
@@ -12800,7 +12800,7 @@
         <v>46144.30592989583</v>
       </c>
       <c r="D72" s="1">
-        <v>46144.55590277778</v>
+        <v>46144.30590277778</v>
       </c>
       <c r="E72">
         <v>32524</v>
@@ -12922,7 +12922,7 @@
         <v>46144.30609672454</v>
       </c>
       <c r="D73" s="1">
-        <v>46144.556076388886</v>
+        <v>46144.306076388886</v>
       </c>
       <c r="E73">
         <v>33010</v>
@@ -13065,7 +13065,7 @@
         <v>46144.306277511576</v>
       </c>
       <c r="D74" s="1">
-        <v>46144.55625</v>
+        <v>46144.30625</v>
       </c>
       <c r="E74">
         <v>33269</v>
@@ -13187,7 +13187,7 @@
         <v>46144.30644429398</v>
       </c>
       <c r="D75" s="1">
-        <v>46144.55642361111</v>
+        <v>46144.30642361111</v>
       </c>
       <c r="E75">
         <v>33752</v>
@@ -13330,7 +13330,7 @@
         <v>46144.306628391205</v>
       </c>
       <c r="D76" s="1">
-        <v>46144.556597222225</v>
+        <v>46144.306597222225</v>
       </c>
       <c r="E76">
         <v>34109</v>
@@ -13452,7 +13452,7 @@
         <v>46144.306791006944</v>
       </c>
       <c r="D77" s="1">
-        <v>46144.55677083333</v>
+        <v>46144.30677083333</v>
       </c>
       <c r="E77">
         <v>34570</v>
@@ -13595,7 +13595,7 @@
         <v>46144.30697153935</v>
       </c>
       <c r="D78" s="1">
-        <v>46144.55694444444</v>
+        <v>46144.30694444444</v>
       </c>
       <c r="E78">
         <v>34873</v>
@@ -13717,7 +13717,7 @@
         <v>46144.307138923614</v>
       </c>
       <c r="D79" s="1">
-        <v>46144.557118055556</v>
+        <v>46144.307118055556</v>
       </c>
       <c r="E79">
         <v>35342</v>
@@ -13860,7 +13860,7 @@
         <v>46144.307318680556</v>
       </c>
       <c r="D80" s="1">
-        <v>46144.557291666664</v>
+        <v>46144.307291666664</v>
       </c>
       <c r="E80">
         <v>35657</v>
@@ -13982,7 +13982,7 @@
         <v>46144.30748542824</v>
       </c>
       <c r="D81" s="1">
-        <v>46144.55746527778</v>
+        <v>46144.30746527778</v>
       </c>
       <c r="E81">
         <v>36112</v>
@@ -14125,7 +14125,7 @@
         <v>46144.30766980324</v>
       </c>
       <c r="D82" s="1">
-        <v>46144.55763888889</v>
+        <v>46144.30763888889</v>
       </c>
       <c r="E82">
         <v>36428</v>
@@ -14247,7 +14247,7 @@
         <v>46144.30783334491</v>
       </c>
       <c r="D83" s="1">
-        <v>46144.5578125</v>
+        <v>46144.3078125</v>
       </c>
       <c r="E83">
         <v>36979</v>
@@ -14390,7 +14390,7 @@
         <v>46144.30801359954</v>
       </c>
       <c r="D84" s="1">
-        <v>46144.55798611111</v>
+        <v>46144.30798611111</v>
       </c>
       <c r="E84">
         <v>37291</v>
@@ -14512,7 +14512,7 @@
         <v>46144.30817986111</v>
       </c>
       <c r="D85" s="1">
-        <v>46144.55815972222</v>
+        <v>46144.30815972222</v>
       </c>
       <c r="E85">
         <v>37823</v>
@@ -14655,7 +14655,7 @@
         <v>46144.30836034722</v>
       </c>
       <c r="D86" s="1">
-        <v>46144.558333333334</v>
+        <v>46144.308333333334</v>
       </c>
       <c r="E86">
         <v>38197</v>
@@ -14777,7 +14777,7 @@
         <v>46144.30852777778</v>
       </c>
       <c r="D87" s="1">
-        <v>46144.55850694444</v>
+        <v>46144.30850694444</v>
       </c>
       <c r="E87">
         <v>38619</v>
@@ -14920,7 +14920,7 @@
         <v>46144.308711805556</v>
       </c>
       <c r="D88" s="1">
-        <v>46144.55868055556</v>
+        <v>46144.30868055556</v>
       </c>
       <c r="E88">
         <v>38870</v>
@@ -15042,7 +15042,7 @@
         <v>46144.30887447917</v>
       </c>
       <c r="D89" s="1">
-        <v>46144.558854166666</v>
+        <v>46144.308854166666</v>
       </c>
       <c r="E89">
         <v>39389</v>
@@ -15185,7 +15185,7 @@
         <v>46144.309055335645</v>
       </c>
       <c r="D90" s="1">
-        <v>46144.55902777778</v>
+        <v>46144.30902777778</v>
       </c>
       <c r="E90">
         <v>39775</v>
@@ -15307,7 +15307,7 @@
         <v>46144.30922215278</v>
       </c>
       <c r="D91" s="1">
-        <v>46144.55920138889</v>
+        <v>46144.30920138889</v>
       </c>
       <c r="E91">
         <v>40259</v>
@@ -15450,7 +15450,7 @@
         <v>46144.3094028125</v>
       </c>
       <c r="D92" s="1">
-        <v>46144.559375</v>
+        <v>46144.309375</v>
       </c>
       <c r="E92">
         <v>40543</v>
@@ -15572,7 +15572,7 @@
         <v>46144.30956864583</v>
       </c>
       <c r="D93" s="1">
-        <v>46144.55954861111</v>
+        <v>46144.30954861111</v>
       </c>
       <c r="E93">
         <v>40951</v>
@@ -15715,7 +15715,7 @@
         <v>46144.30975403935</v>
       </c>
       <c r="D94" s="1">
-        <v>46144.55972222222</v>
+        <v>46144.30972222222</v>
       </c>
       <c r="E94">
         <v>41242</v>
@@ -15837,7 +15837,7 @@
         <v>46144.30991600695</v>
       </c>
       <c r="D95" s="1">
-        <v>46144.559895833336</v>
+        <v>46144.309895833336</v>
       </c>
       <c r="E95">
         <v>41679</v>
@@ -15980,7 +15980,7 @@
         <v>46144.31009626157</v>
       </c>
       <c r="D96" s="1">
-        <v>46144.560069444444</v>
+        <v>46144.310069444444</v>
       </c>
       <c r="E96">
         <v>41915</v>
@@ -16102,7 +16102,7 @@
         <v>46144.31026313658</v>
       </c>
       <c r="D97" s="1">
-        <v>46144.56024305556</v>
+        <v>46144.31024305556</v>
       </c>
       <c r="E97">
         <v>42348</v>
@@ -16245,7 +16245,7 @@
         <v>46144.31044420139</v>
       </c>
       <c r="D98" s="1">
-        <v>46144.56041666667</v>
+        <v>46144.31041666667</v>
       </c>
       <c r="E98">
         <v>42607</v>
@@ -16367,7 +16367,7 @@
         <v>46144.31061049768</v>
       </c>
       <c r="D99" s="1">
-        <v>46144.560590277775</v>
+        <v>46144.310590277775</v>
       </c>
       <c r="E99">
         <v>43098</v>
@@ -16510,7 +16510,7 @@
         <v>46144.31079520833</v>
       </c>
       <c r="D100" s="1">
-        <v>46144.56076388889</v>
+        <v>46144.31076388889</v>
       </c>
       <c r="E100">
         <v>43345</v>
@@ -16632,7 +16632,7 @@
         <v>46144.31095762731</v>
       </c>
       <c r="D101" s="1">
-        <v>46144.5609375</v>
+        <v>46144.3109375</v>
       </c>
       <c r="E101">
         <v>43785</v>
@@ -16775,7 +16775,7 @@
         <v>46144.31113818287</v>
       </c>
       <c r="D102" s="1">
-        <v>46144.561111111114</v>
+        <v>46144.311111111114</v>
       </c>
       <c r="E102">
         <v>44093</v>
@@ -16897,7 +16897,7 @@
         <v>46144.311305219904</v>
       </c>
       <c r="D103" s="1">
-        <v>46144.56128472222</v>
+        <v>46144.31128472222</v>
       </c>
       <c r="E103">
         <v>44500</v>
@@ -17040,7 +17040,7 @@
         <v>46144.311485081016</v>
       </c>
       <c r="D104" s="1">
-        <v>46144.56145833333</v>
+        <v>46144.31145833333</v>
       </c>
       <c r="E104">
         <v>44832</v>
@@ -17162,7 +17162,7 @@
         <v>46144.3116519213</v>
       </c>
       <c r="D105" s="1">
-        <v>46144.561631944445</v>
+        <v>46144.311631944445</v>
       </c>
       <c r="E105">
         <v>45294</v>
@@ -17305,7 +17305,7 @@
         <v>46144.31183613426</v>
       </c>
       <c r="D106" s="1">
-        <v>46144.56180555555</v>
+        <v>46144.31180555555</v>
       </c>
       <c r="E106">
         <v>45590</v>
@@ -17427,7 +17427,7 @@
         <v>46144.311999363425</v>
       </c>
       <c r="D107" s="1">
-        <v>46144.56197916667</v>
+        <v>46144.31197916667</v>
       </c>
       <c r="E107">
         <v>46037</v>
@@ -17570,7 +17570,7 @@
         <v>46144.31218040509</v>
       </c>
       <c r="D108" s="1">
-        <v>46144.56215277778</v>
+        <v>46144.31215277778</v>
       </c>
       <c r="E108">
         <v>46440</v>
@@ -17692,7 +17692,7 @@
         <v>46144.31234725694</v>
       </c>
       <c r="D109" s="1">
-        <v>46144.56232638889</v>
+        <v>46144.31232638889</v>
       </c>
       <c r="E109">
         <v>46823</v>
@@ -17835,7 +17835,7 @@
         <v>46144.31252741898</v>
       </c>
       <c r="D110" s="1">
-        <v>46144.5625</v>
+        <v>46144.3125</v>
       </c>
       <c r="E110">
         <v>46981</v>
@@ -17957,7 +17957,7 @@
         <v>46144.31269449074</v>
       </c>
       <c r="D111" s="1">
-        <v>46144.56267361111</v>
+        <v>46144.31267361111</v>
       </c>
       <c r="E111">
         <v>47271</v>
@@ -18100,7 +18100,7 @@
         <v>46144.31287782407</v>
       </c>
       <c r="D112" s="1">
-        <v>46144.56284722222</v>
+        <v>46144.31284722222</v>
       </c>
       <c r="E112">
         <v>47453</v>
@@ -18222,7 +18222,7 @@
         <v>46144.31304122685</v>
       </c>
       <c r="D113" s="1">
-        <v>46144.56302083333</v>
+        <v>46144.31302083333</v>
       </c>
       <c r="E113">
         <v>47819</v>
@@ -18365,7 +18365,7 @@
         <v>46144.313221979166</v>
       </c>
       <c r="D114" s="1">
-        <v>46144.56319444445</v>
+        <v>46144.31319444445</v>
       </c>
       <c r="E114">
         <v>48031</v>
@@ -18487,7 +18487,7 @@
         <v>46144.31338825232</v>
       </c>
       <c r="D115" s="1">
-        <v>46144.563368055555</v>
+        <v>46144.313368055555</v>
       </c>
       <c r="E115">
         <v>48449</v>
@@ -18630,7 +18630,7 @@
         <v>46144.31356864583</v>
       </c>
       <c r="D116" s="1">
-        <v>46144.56354166667</v>
+        <v>46144.31354166667</v>
       </c>
       <c r="E116">
         <v>48874</v>
@@ -18752,7 +18752,7 @@
         <v>46144.31373578704</v>
       </c>
       <c r="D117" s="1">
-        <v>46144.56371527778</v>
+        <v>46144.31371527778</v>
       </c>
       <c r="E117">
         <v>49382</v>
@@ -18895,7 +18895,7 @@
         <v>46144.313919837965</v>
       </c>
       <c r="D118" s="1">
-        <v>46144.563888888886</v>
+        <v>46144.313888888886</v>
       </c>
       <c r="E118">
         <v>49662</v>
@@ -19017,7 +19017,7 @@
         <v>46144.31408304398</v>
       </c>
       <c r="D119" s="1">
-        <v>46144.5640625</v>
+        <v>46144.3140625</v>
       </c>
       <c r="E119">
         <v>50031</v>
@@ -19160,7 +19160,7 @@
         <v>46144.31426377315</v>
       </c>
       <c r="D120" s="1">
-        <v>46144.56423611111</v>
+        <v>46144.31423611111</v>
       </c>
       <c r="E120">
         <v>50259</v>
@@ -19282,7 +19282,7 @@
         <v>46144.31443346065</v>
       </c>
       <c r="D121" s="1">
-        <v>46144.564409722225</v>
+        <v>46144.314409722225</v>
       </c>
       <c r="E121">
         <v>50616</v>
@@ -19425,7 +19425,7 @@
         <v>46144.31460962963</v>
       </c>
       <c r="D122" s="1">
-        <v>46144.56458333333</v>
+        <v>46144.31458333333</v>
       </c>
       <c r="E122">
         <v>50794</v>
@@ -19547,7 +19547,7 @@
         <v>46144.31477741898</v>
       </c>
       <c r="D123" s="1">
-        <v>46144.56475694444</v>
+        <v>46144.31475694444</v>
       </c>
       <c r="E123">
         <v>51123</v>
@@ -19690,7 +19690,7 @@
         <v>46144.31496149306</v>
       </c>
       <c r="D124" s="1">
-        <v>46144.564930555556</v>
+        <v>46144.314930555556</v>
       </c>
       <c r="E124">
         <v>51483</v>
@@ -19812,7 +19812,7 @@
         <v>46144.31512472222</v>
       </c>
       <c r="D125" s="1">
-        <v>46144.565104166664</v>
+        <v>46144.315104166664</v>
       </c>
       <c r="E125">
         <v>52007</v>
@@ -19955,7 +19955,7 @@
         <v>46144.31530568287</v>
       </c>
       <c r="D126" s="1">
-        <v>46144.56527777778</v>
+        <v>46144.31527777778</v>
       </c>
       <c r="E126">
         <v>52270</v>
@@ -20077,7 +20077,7 @@
         <v>46144.31547175926</v>
       </c>
       <c r="D127" s="1">
-        <v>46144.56545138889</v>
+        <v>46144.31545138889</v>
       </c>
       <c r="E127">
         <v>52824</v>
@@ -20223,7 +20223,7 @@
         <v>46144.31565230324</v>
       </c>
       <c r="D128" s="1">
-        <v>46144.565625</v>
+        <v>46144.315625</v>
       </c>
       <c r="E128">
         <v>52992</v>
@@ -20345,7 +20345,7 @@
         <v>46144.31581886574</v>
       </c>
       <c r="D129" s="1">
-        <v>46144.56579861111</v>
+        <v>46144.31579861111</v>
       </c>
       <c r="E129">
         <v>53320</v>
@@ -20488,7 +20488,7 @@
         <v>46144.316002789354</v>
       </c>
       <c r="D130" s="1">
-        <v>46144.56597222222</v>
+        <v>46144.31597222222</v>
       </c>
       <c r="E130">
         <v>53616</v>
@@ -20610,7 +20610,7 @@
         <v>46144.316165717595</v>
       </c>
       <c r="D131" s="1">
-        <v>46144.566145833334</v>
+        <v>46144.316145833334</v>
       </c>
       <c r="E131">
         <v>53949</v>
@@ -20753,7 +20753,7 @@
         <v>46144.316346377316</v>
       </c>
       <c r="D132" s="1">
-        <v>46144.56631944444</v>
+        <v>46144.31631944444</v>
       </c>
       <c r="E132">
         <v>54137</v>
@@ -20875,7 +20875,7 @@
         <v>46144.316513645834</v>
       </c>
       <c r="D133" s="1">
-        <v>46144.56649305556</v>
+        <v>46144.31649305556</v>
       </c>
       <c r="E133">
         <v>54460</v>
@@ -21018,7 +21018,7 @@
         <v>46144.31669310185</v>
       </c>
       <c r="D134" s="1">
-        <v>46144.566666666666</v>
+        <v>46144.316666666666</v>
       </c>
       <c r="E134">
         <v>54666</v>
@@ -21140,7 +21140,7 @@
         <v>46144.316860300925</v>
       </c>
       <c r="D135" s="1">
-        <v>46144.56684027778</v>
+        <v>46144.31684027778</v>
       </c>
       <c r="E135">
         <v>55014</v>
@@ -21283,7 +21283,7 @@
         <v>46144.31704484954</v>
       </c>
       <c r="D136" s="1">
-        <v>46144.56701388889</v>
+        <v>46144.31701388889</v>
       </c>
       <c r="E136">
         <v>55223</v>
@@ -21405,7 +21405,7 @@
         <v>46144.31721048611</v>
       </c>
       <c r="D137" s="1">
-        <v>46144.5671875</v>
+        <v>46144.3171875</v>
       </c>
       <c r="E137">
         <v>55576</v>
@@ -21548,7 +21548,7 @@
         <v>46144.31738877315</v>
       </c>
       <c r="D138" s="1">
-        <v>46144.56736111111</v>
+        <v>46144.31736111111</v>
       </c>
       <c r="E138">
         <v>55752</v>
@@ -21670,7 +21670,7 @@
         <v>46144.31755526621</v>
       </c>
       <c r="D139" s="1">
-        <v>46144.56753472222</v>
+        <v>46144.31753472222</v>
       </c>
       <c r="E139">
         <v>56106</v>
@@ -21813,7 +21813,7 @@
         <v>46144.31773538194</v>
       </c>
       <c r="D140" s="1">
-        <v>46144.567708333336</v>
+        <v>46144.317708333336</v>
       </c>
       <c r="E140">
         <v>56313</v>
@@ -21935,7 +21935,7 @@
         <v>46144.31790165509</v>
       </c>
       <c r="D141" s="1">
-        <v>46144.567881944444</v>
+        <v>46144.317881944444</v>
       </c>
       <c r="E141">
         <v>56647</v>
@@ -22078,7 +22078,7 @@
         <v>46144.318086527775</v>
       </c>
       <c r="D142" s="1">
-        <v>46144.56805555556</v>
+        <v>46144.31805555556</v>
       </c>
       <c r="E142">
         <v>56838</v>
@@ -22200,7 +22200,7 @@
         <v>46144.318249537035</v>
       </c>
       <c r="D143" s="1">
-        <v>46144.56822916667</v>
+        <v>46144.31822916667</v>
       </c>
       <c r="E143">
         <v>57194</v>
@@ -22343,7 +22343,7 @@
         <v>46144.31843032407</v>
       </c>
       <c r="D144" s="1">
-        <v>46144.568402777775</v>
+        <v>46144.318402777775</v>
       </c>
       <c r="E144">
         <v>57425</v>
@@ -22465,7 +22465,7 @@
         <v>46144.31859934028</v>
       </c>
       <c r="D145" s="1">
-        <v>46144.56857638889</v>
+        <v>46144.31857638889</v>
       </c>
       <c r="E145">
         <v>57770</v>
@@ -22608,7 +22608,7 @@
         <v>46144.31877712963</v>
       </c>
       <c r="D146" s="1">
-        <v>46144.56875</v>
+        <v>46144.31875</v>
       </c>
       <c r="E146">
         <v>57960</v>
@@ -22730,7 +22730,7 @@
         <v>46144.31894386574</v>
       </c>
       <c r="D147" s="1">
-        <v>46144.568923611114</v>
+        <v>46144.318923611114</v>
       </c>
       <c r="E147">
         <v>58311</v>
@@ -22873,7 +22873,7 @@
         <v>46144.31912820602</v>
       </c>
       <c r="D148" s="1">
-        <v>46144.56909722222</v>
+        <v>46144.31909722222</v>
       </c>
       <c r="E148">
         <v>58518</v>
@@ -22995,7 +22995,7 @@
         <v>46144.319290775464</v>
       </c>
       <c r="D149" s="1">
-        <v>46144.56927083333</v>
+        <v>46144.31927083333</v>
       </c>
       <c r="E149">
         <v>58861</v>
@@ -23138,7 +23138,7 @@
         <v>46144.319471944444</v>
       </c>
       <c r="D150" s="1">
-        <v>46144.569444444445</v>
+        <v>46144.319444444445</v>
       </c>
       <c r="E150">
         <v>59076</v>
@@ -23260,7 +23260,7 @@
         <v>46144.31963770834</v>
       </c>
       <c r="D151" s="1">
-        <v>46144.56961805555</v>
+        <v>46144.31961805555</v>
       </c>
       <c r="E151">
         <v>59490</v>
@@ -23403,7 +23403,7 @@
         <v>46144.31981853009</v>
       </c>
       <c r="D152" s="1">
-        <v>46144.56979166667</v>
+        <v>46144.31979166667</v>
       </c>
       <c r="E152">
         <v>59702</v>
@@ -23525,7 +23525,7 @@
         <v>46144.31998552084</v>
       </c>
       <c r="D153" s="1">
-        <v>46144.56996527778</v>
+        <v>46144.31996527778</v>
       </c>
       <c r="E153">
         <v>60057</v>
@@ -23668,7 +23668,7 @@
         <v>46144.320170266205</v>
       </c>
       <c r="D154" s="1">
-        <v>46144.57013888889</v>
+        <v>46144.32013888889</v>
       </c>
       <c r="E154">
         <v>60257</v>
@@ -23790,7 +23790,7 @@
         <v>46144.3203325463</v>
       </c>
       <c r="D155" s="1">
-        <v>46144.5703125</v>
+        <v>46144.3203125</v>
       </c>
       <c r="E155">
         <v>60587</v>
@@ -23933,7 +23933,7 @@
         <v>46144.32051372685</v>
       </c>
       <c r="D156" s="1">
-        <v>46144.57048611111</v>
+        <v>46144.32048611111</v>
       </c>
       <c r="E156">
         <v>60779</v>
@@ -24055,7 +24055,7 @@
         <v>46144.32067971065</v>
       </c>
       <c r="D157" s="1">
-        <v>46144.57065972222</v>
+        <v>46144.32065972222</v>
       </c>
       <c r="E157">
         <v>61132</v>
@@ -24198,7 +24198,7 @@
         <v>46144.32086105324</v>
       </c>
       <c r="D158" s="1">
-        <v>46144.57083333333</v>
+        <v>46144.32083333333</v>
       </c>
       <c r="E158">
         <v>61323</v>
@@ -24320,7 +24320,7 @@
         <v>46144.32102751157</v>
       </c>
       <c r="D159" s="1">
-        <v>46144.57100694445</v>
+        <v>46144.32100694445</v>
       </c>
       <c r="E159">
         <v>61663</v>
@@ -24463,7 +24463,7 @@
         <v>46144.3212115625</v>
       </c>
       <c r="D160" s="1">
-        <v>46144.571180555555</v>
+        <v>46144.321180555555</v>
       </c>
       <c r="E160">
         <v>61861</v>
@@ -24585,7 +24585,7 @@
         <v>46144.321374618055</v>
       </c>
       <c r="D161" s="1">
-        <v>46144.57135416667</v>
+        <v>46144.32135416667</v>
       </c>
       <c r="E161">
         <v>62195</v>
@@ -24728,7 +24728,7 @@
         <v>46144.32172202547</v>
       </c>
       <c r="D162" s="1">
-        <v>46144.571701388886</v>
+        <v>46144.321701388886</v>
       </c>
       <c r="E162">
         <v>62731</v>
@@ -24871,7 +24871,7 @@
         <v>46144.321902662035</v>
       </c>
       <c r="D163" s="1">
-        <v>46144.571875</v>
+        <v>46144.321875</v>
       </c>
       <c r="E163">
         <v>62915</v>
@@ -24993,7 +24993,7 @@
         <v>46144.32206871528</v>
       </c>
       <c r="D164" s="1">
-        <v>46144.57204861111</v>
+        <v>46144.32204861111</v>
       </c>
       <c r="E164">
         <v>63295</v>
@@ -25136,7 +25136,7 @@
         <v>46144.32225011574</v>
       </c>
       <c r="D165" s="1">
-        <v>46144.572222222225</v>
+        <v>46144.322222222225</v>
       </c>
       <c r="E165">
         <v>63482</v>
@@ -25258,7 +25258,7 @@
         <v>46144.32241579861</v>
       </c>
       <c r="D166" s="1">
-        <v>46144.57239583333</v>
+        <v>46144.32239583333</v>
       </c>
       <c r="E166">
         <v>63819</v>
@@ -25401,7 +25401,7 @@
         <v>46144.322600520834</v>
       </c>
       <c r="D167" s="1">
-        <v>46144.57256944444</v>
+        <v>46144.32256944444</v>
       </c>
       <c r="E167">
         <v>64037</v>
@@ -25523,7 +25523,7 @@
         <v>46144.32276303241</v>
       </c>
       <c r="D168" s="1">
-        <v>46144.572743055556</v>
+        <v>46144.322743055556</v>
       </c>
       <c r="E168">
         <v>64397</v>
@@ -25666,7 +25666,7 @@
         <v>46144.32294395833</v>
       </c>
       <c r="D169" s="1">
-        <v>46144.572916666664</v>
+        <v>46144.322916666664</v>
       </c>
       <c r="E169">
         <v>64608</v>
@@ -25788,7 +25788,7 @@
         <v>46144.323110868056</v>
       </c>
       <c r="D170" s="1">
-        <v>46144.57309027778</v>
+        <v>46144.32309027778</v>
       </c>
       <c r="E170">
         <v>64960</v>
@@ -25931,7 +25931,7 @@
         <v>46144.32329113426</v>
       </c>
       <c r="D171" s="1">
-        <v>46144.57326388889</v>
+        <v>46144.32326388889</v>
       </c>
       <c r="E171">
         <v>65185</v>
@@ -26053,7 +26053,7 @@
         <v>46144.323457847226</v>
       </c>
       <c r="D172" s="1">
-        <v>46144.5734375</v>
+        <v>46144.3234375</v>
       </c>
       <c r="E172">
         <v>65536</v>
@@ -26196,7 +26196,7 @@
         <v>46144.32364174769</v>
       </c>
       <c r="D173" s="1">
-        <v>46144.57361111111</v>
+        <v>46144.32361111111</v>
       </c>
       <c r="E173">
         <v>65789</v>
@@ -26318,7 +26318,7 @@
         <v>46144.32380542824</v>
       </c>
       <c r="D174" s="1">
-        <v>46144.57378472222</v>
+        <v>46144.32378472222</v>
       </c>
       <c r="E174">
         <v>66154</v>
@@ -26461,7 +26461,7 @@
         <v>46144.32398543981</v>
       </c>
       <c r="D175" s="1">
-        <v>46144.573958333334</v>
+        <v>46144.323958333334</v>
       </c>
       <c r="E175">
         <v>66360</v>
@@ -26583,7 +26583,7 @@
         <v>46144.324151863424</v>
       </c>
       <c r="D176" s="1">
-        <v>46144.57413194444</v>
+        <v>46144.32413194444</v>
       </c>
       <c r="E176">
         <v>66714</v>
@@ -26726,7 +26726,7 @@
         <v>46144.32433215278</v>
       </c>
       <c r="D177" s="1">
-        <v>46144.57430555556</v>
+        <v>46144.32430555556</v>
       </c>
       <c r="E177">
         <v>66931</v>
@@ -26848,7 +26848,7 @@
         <v>46144.32449962963</v>
       </c>
       <c r="D178" s="1">
-        <v>46144.574479166666</v>
+        <v>46144.324479166666</v>
       </c>
       <c r="E178">
         <v>67283</v>
@@ -26991,7 +26991,7 @@
         <v>46144.32468347222</v>
       </c>
       <c r="D179" s="1">
-        <v>46144.57465277778</v>
+        <v>46144.32465277778</v>
       </c>
       <c r="E179">
         <v>67482</v>
@@ -27113,7 +27113,7 @@
         <v>46144.32484649306</v>
       </c>
       <c r="D180" s="1">
-        <v>46144.57482638889</v>
+        <v>46144.32482638889</v>
       </c>
       <c r="E180">
         <v>67834</v>
@@ -27256,7 +27256,7 @@
         <v>46144.3250271412</v>
       </c>
       <c r="D181" s="1">
-        <v>46144.575</v>
+        <v>46144.325</v>
       </c>
       <c r="E181">
         <v>68037</v>
@@ -27378,7 +27378,7 @@
         <v>46144.325193958335</v>
       </c>
       <c r="D182" s="1">
-        <v>46144.57517361111</v>
+        <v>46144.32517361111</v>
       </c>
       <c r="E182">
         <v>68398</v>
@@ -27521,7 +27521,7 @@
         <v>46144.32537409722</v>
       </c>
       <c r="D183" s="1">
-        <v>46144.57534722222</v>
+        <v>46144.32534722222</v>
       </c>
       <c r="E183">
         <v>68611</v>
@@ -27643,7 +27643,7 @@
         <v>46144.32554039352</v>
       </c>
       <c r="D184" s="1">
-        <v>46144.575520833336</v>
+        <v>46144.325520833336</v>
       </c>
       <c r="E184">
         <v>68958</v>
@@ -27786,7 +27786,7 @@
         <v>46144.325724953706</v>
       </c>
       <c r="D185" s="1">
-        <v>46144.575694444444</v>
+        <v>46144.325694444444</v>
       </c>
       <c r="E185">
         <v>69143</v>
@@ -27908,7 +27908,7 @@
         <v>46144.32588832176</v>
       </c>
       <c r="D186" s="1">
-        <v>46144.57586805556</v>
+        <v>46144.32586805556</v>
       </c>
       <c r="E186">
         <v>69501</v>
@@ -28051,7 +28051,7 @@
         <v>46144.326068773145</v>
       </c>
       <c r="D187" s="1">
-        <v>46144.57604166667</v>
+        <v>46144.32604166667</v>
       </c>
       <c r="E187">
         <v>69713</v>
@@ -28173,7 +28173,7 @@
         <v>46144.326235960645</v>
       </c>
       <c r="D188" s="1">
-        <v>46144.576215277775</v>
+        <v>46144.326215277775</v>
       </c>
       <c r="E188">
         <v>70082</v>
@@ -28316,7 +28316,7 @@
         <v>46144.326415752315</v>
       </c>
       <c r="D189" s="1">
-        <v>46144.57638888889</v>
+        <v>46144.32638888889</v>
       </c>
       <c r="E189">
         <v>70317</v>
@@ -28438,7 +28438,7 @@
         <v>46144.326583263886</v>
       </c>
       <c r="D190" s="1">
-        <v>46144.5765625</v>
+        <v>46144.3265625</v>
       </c>
       <c r="E190">
         <v>70674</v>
@@ -28581,7 +28581,7 @@
         <v>46144.32676658565</v>
       </c>
       <c r="D191" s="1">
-        <v>46144.576736111114</v>
+        <v>46144.326736111114</v>
       </c>
       <c r="E191">
         <v>70895</v>
@@ -28703,7 +28703,7 @@
         <v>46144.32693041667</v>
       </c>
       <c r="D192" s="1">
-        <v>46144.57690972222</v>
+        <v>46144.32690972222</v>
       </c>
       <c r="E192">
         <v>71254</v>
@@ -28846,7 +28846,7 @@
         <v>46144.32711027778</v>
       </c>
       <c r="D193" s="1">
-        <v>46144.57708333333</v>
+        <v>46144.32708333333</v>
       </c>
       <c r="E193">
         <v>71459</v>
@@ -28968,7 +28968,7 @@
         <v>46144.32727806713</v>
       </c>
       <c r="D194" s="1">
-        <v>46144.577256944445</v>
+        <v>46144.327256944445</v>
       </c>
       <c r="E194">
         <v>71806</v>
@@ -29111,7 +29111,7 @@
         <v>46144.3274584375</v>
       </c>
       <c r="D195" s="1">
-        <v>46144.57743055555</v>
+        <v>46144.32743055555</v>
       </c>
       <c r="E195">
         <v>72020</v>
@@ -29233,7 +29233,7 @@
         <v>46144.32762438658</v>
       </c>
       <c r="D196" s="1">
-        <v>46144.57760416667</v>
+        <v>46144.32760416667</v>
       </c>
       <c r="E196">
         <v>72375</v>
@@ -29376,7 +29376,7 @@
         <v>46144.32780806713</v>
       </c>
       <c r="D197" s="1">
-        <v>46144.57777777778</v>
+        <v>46144.32777777778</v>
       </c>
       <c r="E197">
         <v>72568</v>
@@ -29498,7 +29498,7 @@
         <v>46144.32797144676</v>
       </c>
       <c r="D198" s="1">
-        <v>46144.57795138889</v>
+        <v>46144.32795138889</v>
       </c>
       <c r="E198">
         <v>72897</v>
@@ -29641,7 +29641,7 @@
         <v>46144.32815233796</v>
       </c>
       <c r="D199" s="1">
-        <v>46144.578125</v>
+        <v>46144.328125</v>
       </c>
       <c r="E199">
         <v>73083</v>
@@ -29763,7 +29763,7 @@
         <v>46144.32831805556</v>
       </c>
       <c r="D200" s="1">
-        <v>46144.57829861111</v>
+        <v>46144.32829861111</v>
       </c>
       <c r="E200">
         <v>73447</v>
@@ -29906,7 +29906,7 @@
         <v>46144.32849943287</v>
       </c>
       <c r="D201" s="1">
-        <v>46144.57847222222</v>
+        <v>46144.32847222222</v>
       </c>
       <c r="E201">
         <v>73644</v>
@@ -30028,7 +30028,7 @@
         <v>46144.32866663195</v>
       </c>
       <c r="D202" s="1">
-        <v>46144.57864583333</v>
+        <v>46144.32864583333</v>
       </c>
       <c r="E202">
         <v>73999</v>
@@ -30171,7 +30171,7 @@
         <v>46144.32885092593</v>
       </c>
       <c r="D203" s="1">
-        <v>46144.57881944445</v>
+        <v>46144.32881944445</v>
       </c>
       <c r="E203">
         <v>74199</v>
@@ -30293,7 +30293,7 @@
         <v>46144.32901311343</v>
       </c>
       <c r="D204" s="1">
-        <v>46144.578993055555</v>
+        <v>46144.328993055555</v>
       </c>
       <c r="E204">
         <v>74558</v>
@@ -30436,7 +30436,7 @@
         <v>46144.329193564816</v>
       </c>
       <c r="D205" s="1">
-        <v>46144.57916666667</v>
+        <v>46144.32916666667</v>
       </c>
       <c r="E205">
         <v>74822</v>
@@ -30558,7 +30558,7 @@
         <v>46144.329359965275</v>
       </c>
       <c r="D206" s="1">
-        <v>46144.57934027778</v>
+        <v>46144.32934027778</v>
       </c>
       <c r="E206">
         <v>75202</v>
@@ -30701,7 +30701,7 @@
         <v>46144.32954125</v>
       </c>
       <c r="D207" s="1">
-        <v>46144.579513888886</v>
+        <v>46144.329513888886</v>
       </c>
       <c r="E207">
         <v>75433</v>
@@ -30823,7 +30823,7 @@
         <v>46144.32970773148</v>
       </c>
       <c r="D208" s="1">
-        <v>46144.5796875</v>
+        <v>46144.3296875</v>
       </c>
       <c r="E208">
         <v>75821</v>
@@ -30966,7 +30966,7 @@
         <v>46144.329891863425</v>
       </c>
       <c r="D209" s="1">
-        <v>46144.57986111111</v>
+        <v>46144.32986111111</v>
       </c>
       <c r="E209">
         <v>76040</v>
@@ -31088,7 +31088,7 @@
         <v>46144.33005484954</v>
       </c>
       <c r="D210" s="1">
-        <v>46144.580034722225</v>
+        <v>46144.330034722225</v>
       </c>
       <c r="E210">
         <v>76405</v>
@@ -31231,7 +31231,7 @@
         <v>46144.330235532405</v>
       </c>
       <c r="D211" s="1">
-        <v>46144.58020833333</v>
+        <v>46144.33020833333</v>
       </c>
       <c r="E211">
         <v>76620</v>
@@ -31353,7 +31353,7 @@
         <v>46144.33040195602</v>
       </c>
       <c r="D212" s="1">
-        <v>46144.58038194444</v>
+        <v>46144.33038194444</v>
       </c>
       <c r="E212">
         <v>77021</v>
@@ -31496,7 +31496,7 @@
         <v>46144.330582835646</v>
       </c>
       <c r="D213" s="1">
-        <v>46144.580555555556</v>
+        <v>46144.330555555556</v>
       </c>
       <c r="E213">
         <v>77241</v>
@@ -31618,7 +31618,7 @@
         <v>46144.33074900463</v>
       </c>
       <c r="D214" s="1">
-        <v>46144.580729166664</v>
+        <v>46144.330729166664</v>
       </c>
       <c r="E214">
         <v>77624</v>
@@ -31761,7 +31761,7 @@
         <v>46144.33093393518</v>
       </c>
       <c r="D215" s="1">
-        <v>46144.58090277778</v>
+        <v>46144.33090277778</v>
       </c>
       <c r="E215">
         <v>77828</v>
@@ -31883,7 +31883,7 @@
         <v>46144.33109702546</v>
       </c>
       <c r="D216" s="1">
-        <v>46144.58107638889</v>
+        <v>46144.33107638889</v>
       </c>
       <c r="E216">
         <v>78222</v>
@@ -32026,7 +32026,7 @@
         <v>46144.33127726852</v>
       </c>
       <c r="D217" s="1">
-        <v>46144.58125</v>
+        <v>46144.33125</v>
       </c>
       <c r="E217">
         <v>78432</v>
@@ -32148,7 +32148,7 @@
         <v>46144.33144446759</v>
       </c>
       <c r="D218" s="1">
-        <v>46144.58142361111</v>
+        <v>46144.33142361111</v>
       </c>
       <c r="E218">
         <v>78814</v>
@@ -32291,7 +32291,7 @@
         <v>46144.33162428241</v>
       </c>
       <c r="D219" s="1">
-        <v>46144.58159722222</v>
+        <v>46144.33159722222</v>
       </c>
       <c r="E219">
         <v>79065</v>
@@ -32413,7 +32413,7 @@
         <v>46144.331790625</v>
       </c>
       <c r="D220" s="1">
-        <v>46144.581770833334</v>
+        <v>46144.331770833334</v>
       </c>
       <c r="E220">
         <v>79432</v>
@@ -32556,7 +32556,7 @@
         <v>46144.3319755787</v>
       </c>
       <c r="D221" s="1">
-        <v>46144.58194444444</v>
+        <v>46144.33194444444</v>
       </c>
       <c r="E221">
         <v>79649</v>
@@ -32678,7 +32678,7 @@
         <v>46144.332138391204</v>
       </c>
       <c r="D222" s="1">
-        <v>46144.58211805556</v>
+        <v>46144.33211805556</v>
       </c>
       <c r="E222">
         <v>80019</v>
@@ -32821,7 +32821,7 @@
         <v>46144.33231925926</v>
       </c>
       <c r="D223" s="1">
-        <v>46144.582291666666</v>
+        <v>46144.332291666666</v>
       </c>
       <c r="E223">
         <v>80253</v>
@@ -32943,7 +32943,7 @@
         <v>46144.33248505787</v>
       </c>
       <c r="D224" s="1">
-        <v>46144.58246527778</v>
+        <v>46144.33246527778</v>
       </c>
       <c r="E224">
         <v>80608</v>
@@ -33086,7 +33086,7 @@
         <v>46144.332666574075</v>
       </c>
       <c r="D225" s="1">
-        <v>46144.58263888889</v>
+        <v>46144.33263888889</v>
       </c>
       <c r="E225">
         <v>80817</v>
@@ -33208,7 +33208,7 @@
         <v>46144.3328337037</v>
       </c>
       <c r="D226" s="1">
-        <v>46144.5828125</v>
+        <v>46144.3328125</v>
       </c>
       <c r="E226">
         <v>81183</v>
@@ -33351,7 +33351,7 @@
         <v>46144.333016909724</v>
       </c>
       <c r="D227" s="1">
-        <v>46144.58298611111</v>
+        <v>46144.33298611111</v>
       </c>
       <c r="E227">
         <v>81411</v>
@@ -33473,7 +33473,7 @@
         <v>46144.333180023146</v>
       </c>
       <c r="D228" s="1">
-        <v>46144.58315972222</v>
+        <v>46144.33315972222</v>
       </c>
       <c r="E228">
         <v>81794</v>
@@ -33616,7 +33616,7 @@
         <v>46144.33336045139</v>
       </c>
       <c r="D229" s="1">
-        <v>46144.583333333336</v>
+        <v>46144.333333333336</v>
       </c>
       <c r="E229">
         <v>82015</v>
@@ -33738,7 +33738,7 @@
         <v>46144.3335275</v>
       </c>
       <c r="D230" s="1">
-        <v>46144.583506944444</v>
+        <v>46144.333506944444</v>
       </c>
       <c r="E230">
         <v>82392</v>
@@ -33881,7 +33881,7 @@
         <v>46144.33370811342</v>
       </c>
       <c r="D231" s="1">
-        <v>46144.58368055556</v>
+        <v>46144.33368055556</v>
       </c>
       <c r="E231">
         <v>82625</v>
@@ -34003,7 +34003,7 @@
         <v>46144.333874421296</v>
       </c>
       <c r="D232" s="1">
-        <v>46144.58385416667</v>
+        <v>46144.33385416667</v>
       </c>
       <c r="E232">
         <v>83003</v>
@@ -34146,7 +34146,7 @@
         <v>46144.334058541666</v>
       </c>
       <c r="D233" s="1">
-        <v>46144.584027777775</v>
+        <v>46144.334027777775</v>
       </c>
       <c r="E233">
         <v>83222</v>
@@ -34268,7 +34268,7 @@
         <v>46144.334221412035</v>
       </c>
       <c r="D234" s="1">
-        <v>46144.58420138889</v>
+        <v>46144.33420138889</v>
       </c>
       <c r="E234">
         <v>83617</v>
@@ -34411,7 +34411,7 @@
         <v>46144.334401886576</v>
       </c>
       <c r="D235" s="1">
-        <v>46144.584375</v>
+        <v>46144.334375</v>
       </c>
       <c r="E235">
         <v>83839</v>
@@ -34533,7 +34533,7 @@
         <v>46144.334568819446</v>
       </c>
       <c r="D236" s="1">
-        <v>46144.584548611114</v>
+        <v>46144.334548611114</v>
       </c>
       <c r="E236">
         <v>84194</v>
@@ -34676,7 +34676,7 @@
         <v>46144.334749016205</v>
       </c>
       <c r="D237" s="1">
-        <v>46144.58472222222</v>
+        <v>46144.33472222222</v>
       </c>
       <c r="E237">
         <v>84430</v>
@@ -34798,7 +34798,7 @@
         <v>46144.33491585648</v>
       </c>
       <c r="D238" s="1">
-        <v>46144.58489583333</v>
+        <v>46144.33489583333</v>
       </c>
       <c r="E238">
         <v>84786</v>
@@ -34941,7 +34941,7 @@
         <v>46144.33509988426</v>
       </c>
       <c r="D239" s="1">
-        <v>46144.585069444445</v>
+        <v>46144.335069444445</v>
       </c>
       <c r="E239">
         <v>85017</v>
@@ -35063,7 +35063,7 @@
         <v>46144.33526325232</v>
       </c>
       <c r="D240" s="1">
-        <v>46144.58524305555</v>
+        <v>46144.33524305555</v>
       </c>
       <c r="E240">
         <v>85399</v>
@@ -35206,7 +35206,7 @@
         <v>46144.33544400463</v>
       </c>
       <c r="D241" s="1">
-        <v>46144.58541666667</v>
+        <v>46144.33541666667</v>
       </c>
       <c r="E241">
         <v>85611</v>
@@ -35328,7 +35328,7 @@
         <v>46144.335610104165</v>
       </c>
       <c r="D242" s="1">
-        <v>46144.58559027778</v>
+        <v>46144.33559027778</v>
       </c>
       <c r="E242">
         <v>85970</v>
@@ -35471,7 +35471,7 @@
         <v>46144.33579099537</v>
       </c>
       <c r="D243" s="1">
-        <v>46144.58576388889</v>
+        <v>46144.33576388889</v>
       </c>
       <c r="E243">
         <v>86192</v>
@@ -35593,7 +35593,7 @@
         <v>46144.33595821759</v>
       </c>
       <c r="D244" s="1">
-        <v>46144.5859375</v>
+        <v>46144.3359375</v>
       </c>
       <c r="E244">
         <v>86567</v>
@@ -35736,7 +35736,7 @@
         <v>46144.336142291664</v>
       </c>
       <c r="D245" s="1">
-        <v>46144.58611111111</v>
+        <v>46144.33611111111</v>
       </c>
       <c r="E245">
         <v>86746</v>
@@ -35858,7 +35858,7 @@
         <v>46144.336304641205</v>
       </c>
       <c r="D246" s="1">
-        <v>46144.58628472222</v>
+        <v>46144.33628472222</v>
       </c>
       <c r="E246">
         <v>87136</v>
@@ -36001,7 +36001,7 @@
         <v>46144.33648521991</v>
       </c>
       <c r="D247" s="1">
-        <v>46144.58645833333</v>
+        <v>46144.33645833333</v>
       </c>
       <c r="E247">
         <v>87357</v>
@@ -36123,7 +36123,7 @@
         <v>46144.33665233797</v>
       </c>
       <c r="D248" s="1">
-        <v>46144.58663194445</v>
+        <v>46144.33663194445</v>
       </c>
       <c r="E248">
         <v>87713</v>
@@ -36266,7 +36266,7 @@
         <v>46144.336832685185</v>
       </c>
       <c r="D249" s="1">
-        <v>46144.586805555555</v>
+        <v>46144.336805555555</v>
       </c>
       <c r="E249">
         <v>87924</v>
@@ -36388,7 +36388,7 @@
         <v>46144.33699989584</v>
       </c>
       <c r="D250" s="1">
-        <v>46144.58697916667</v>
+        <v>46144.33697916667</v>
       </c>
       <c r="E250">
         <v>88294</v>
@@ -36531,7 +36531,7 @@
         <v>46144.33718362269</v>
       </c>
       <c r="D251" s="1">
-        <v>46144.58715277778</v>
+        <v>46144.33715277778</v>
       </c>
       <c r="E251">
         <v>88499</v>
@@ -36653,7 +36653,7 @@
         <v>46144.33734643518</v>
       </c>
       <c r="D252" s="1">
-        <v>46144.587326388886</v>
+        <v>46144.337326388886</v>
       </c>
       <c r="E252">
         <v>88865</v>
@@ -36796,7 +36796,7 @@
         <v>46144.337526944444</v>
       </c>
       <c r="D253" s="1">
-        <v>46144.5875</v>
+        <v>46144.3375</v>
       </c>
       <c r="E253">
         <v>89063</v>
@@ -37074,7 +37074,7 @@
         <v>46144.337804282404</v>
       </c>
       <c r="D2" s="1">
-        <v>46144.58767361111</v>
+        <v>46144.33767361111</v>
       </c>
       <c r="E2">
         <v>88592</v>
@@ -37181,7 +37181,7 @@
         <v>46144.33787456019</v>
       </c>
       <c r="D3" s="1">
-        <v>46144.587847222225</v>
+        <v>46144.337847222225</v>
       </c>
       <c r="E3">
         <v>87068</v>
@@ -37291,7 +37291,7 @@
         <v>46144.33810177083</v>
       </c>
       <c r="D4" s="1">
-        <v>46144.58802083333</v>
+        <v>46144.33802083333</v>
       </c>
       <c r="E4">
         <v>85500</v>
@@ -37434,7 +37434,7 @@
         <v>46144.33822511574</v>
       </c>
       <c r="D5" s="1">
-        <v>46144.58819444444</v>
+        <v>46144.33819444444</v>
       </c>
       <c r="E5">
         <v>84115</v>
@@ -37556,7 +37556,7 @@
         <v>46144.33838840278</v>
       </c>
       <c r="D6" s="1">
-        <v>46144.588368055556</v>
+        <v>46144.338368055556</v>
       </c>
       <c r="E6">
         <v>82693</v>
@@ -37699,7 +37699,7 @@
         <v>46144.33856928241</v>
       </c>
       <c r="D7" s="1">
-        <v>46144.588541666664</v>
+        <v>46144.338541666664</v>
       </c>
       <c r="E7">
         <v>81401</v>
@@ -37821,7 +37821,7 @@
         <v>46144.33873523148</v>
       </c>
       <c r="D8" s="1">
-        <v>46144.58871527778</v>
+        <v>46144.33871527778</v>
       </c>
       <c r="E8">
         <v>80059</v>
@@ -37964,7 +37964,7 @@
         <v>46144.33891677083</v>
       </c>
       <c r="D9" s="1">
-        <v>46144.58888888889</v>
+        <v>46144.33888888889</v>
       </c>
       <c r="E9">
         <v>78812</v>
@@ -38086,7 +38086,7 @@
         <v>46144.33908255787</v>
       </c>
       <c r="D10" s="1">
-        <v>46144.5890625</v>
+        <v>46144.3390625</v>
       </c>
       <c r="E10">
         <v>77687</v>
@@ -38229,7 +38229,7 @@
         <v>46144.33926688657</v>
       </c>
       <c r="D11" s="1">
-        <v>46144.58923611111</v>
+        <v>46144.33923611111</v>
       </c>
       <c r="E11">
         <v>76584</v>
@@ -38351,7 +38351,7 @@
         <v>46144.33942956018</v>
       </c>
       <c r="D12" s="1">
-        <v>46144.58940972222</v>
+        <v>46144.33940972222</v>
       </c>
       <c r="E12">
         <v>75519</v>
@@ -38494,7 +38494,7 @@
         <v>46144.33960998843</v>
       </c>
       <c r="D13" s="1">
-        <v>46144.589583333334</v>
+        <v>46144.339583333334</v>
       </c>
       <c r="E13">
         <v>74530</v>
@@ -38616,7 +38616,7 @@
         <v>46144.33977733796</v>
       </c>
       <c r="D14" s="1">
-        <v>46144.58975694444</v>
+        <v>46144.33975694444</v>
       </c>
       <c r="E14">
         <v>73508</v>
@@ -38759,7 +38759,7 @@
         <v>46144.33995715278</v>
       </c>
       <c r="D15" s="1">
-        <v>46144.58993055556</v>
+        <v>46144.33993055556</v>
       </c>
       <c r="E15">
         <v>72450</v>
@@ -38881,7 +38881,7 @@
         <v>46144.34012424768</v>
       </c>
       <c r="D16" s="1">
-        <v>46144.590104166666</v>
+        <v>46144.340104166666</v>
       </c>
       <c r="E16">
         <v>71476</v>
@@ -39024,7 +39024,7 @@
         <v>46144.34030909722</v>
       </c>
       <c r="D17" s="1">
-        <v>46144.59027777778</v>
+        <v>46144.34027777778</v>
       </c>
       <c r="E17">
         <v>70537</v>
@@ -39146,7 +39146,7 @@
         <v>46144.3404719213</v>
       </c>
       <c r="D18" s="1">
-        <v>46144.59045138889</v>
+        <v>46144.34045138889</v>
       </c>
       <c r="E18">
         <v>69619</v>
@@ -39289,7 +39289,7 @@
         <v>46144.340651481485</v>
       </c>
       <c r="D19" s="1">
-        <v>46144.590625</v>
+        <v>46144.340625</v>
       </c>
       <c r="E19">
         <v>68703</v>
@@ -39411,7 +39411,7 @@
         <v>46144.34081954861</v>
       </c>
       <c r="D20" s="1">
-        <v>46144.59079861111</v>
+        <v>46144.34079861111</v>
       </c>
       <c r="E20">
         <v>67839</v>
@@ -39554,7 +39554,7 @@
         <v>46144.340999479165</v>
       </c>
       <c r="D21" s="1">
-        <v>46144.59097222222</v>
+        <v>46144.34097222222</v>
       </c>
       <c r="E21">
         <v>66964</v>
@@ -39676,7 +39676,7 @@
         <v>46144.34116616898</v>
       </c>
       <c r="D22" s="1">
-        <v>46144.591145833336</v>
+        <v>46144.341145833336</v>
       </c>
       <c r="E22">
         <v>66143</v>
@@ -39819,7 +39819,7 @@
         <v>46144.34135009259</v>
       </c>
       <c r="D23" s="1">
-        <v>46144.591319444444</v>
+        <v>46144.341319444444</v>
       </c>
       <c r="E23">
         <v>65333</v>
@@ -39941,7 +39941,7 @@
         <v>46144.34151681713</v>
       </c>
       <c r="D24" s="1">
-        <v>46144.59149305556</v>
+        <v>46144.34149305556</v>
       </c>
       <c r="E24">
         <v>64548</v>
@@ -40084,7 +40084,7 @@
         <v>46144.34169431713</v>
       </c>
       <c r="D25" s="1">
-        <v>46144.59166666667</v>
+        <v>46144.34166666667</v>
       </c>
       <c r="E25">
         <v>63761</v>
@@ -40206,7 +40206,7 @@
         <v>46144.34186085648</v>
       </c>
       <c r="D26" s="1">
-        <v>46144.591840277775</v>
+        <v>46144.341840277775</v>
       </c>
       <c r="E26">
         <v>63027</v>
@@ -40349,7 +40349,7 @@
         <v>46144.34204134259</v>
       </c>
       <c r="D27" s="1">
-        <v>46144.59201388889</v>
+        <v>46144.34201388889</v>
       </c>
       <c r="E27">
         <v>62272</v>
@@ -40471,7 +40471,7 @@
         <v>46144.34255476852</v>
       </c>
       <c r="D28" s="1">
-        <v>46144.59253472222</v>
+        <v>46144.34253472222</v>
       </c>
       <c r="E28">
         <v>60143</v>
@@ -40614,7 +40614,7 @@
         <v>46144.342739594904</v>
       </c>
       <c r="D29" s="1">
-        <v>46144.59270833333</v>
+        <v>46144.34270833333</v>
       </c>
       <c r="E29">
         <v>59407</v>
@@ -40736,7 +40736,7 @@
         <v>46144.34290221065</v>
       </c>
       <c r="D30" s="1">
-        <v>46144.592881944445</v>
+        <v>46144.342881944445</v>
       </c>
       <c r="E30">
         <v>58754</v>
@@ -40879,7 +40879,7 @@
         <v>46144.343082997686</v>
       </c>
       <c r="D31" s="1">
-        <v>46144.59305555555</v>
+        <v>46144.34305555555</v>
       </c>
       <c r="E31">
         <v>58081</v>
@@ -41001,7 +41001,7 @@
         <v>46144.34342989583</v>
       </c>
       <c r="D32" s="1">
-        <v>46144.59340277778</v>
+        <v>46144.34340277778</v>
       </c>
       <c r="E32">
         <v>56805</v>
@@ -41123,7 +41123,7 @@
         <v>46144.34359701389</v>
       </c>
       <c r="D33" s="1">
-        <v>46144.59357638889</v>
+        <v>46144.34357638889</v>
       </c>
       <c r="E33">
         <v>56202</v>
@@ -41266,7 +41266,7 @@
         <v>46144.34378030093</v>
       </c>
       <c r="D34" s="1">
-        <v>46144.59375</v>
+        <v>46144.34375</v>
       </c>
       <c r="E34">
         <v>55542</v>
@@ -41388,7 +41388,7 @@
         <v>46144.34394412037</v>
       </c>
       <c r="D35" s="1">
-        <v>46144.59392361111</v>
+        <v>46144.34392361111</v>
       </c>
       <c r="E35">
         <v>54974</v>
@@ -41531,7 +41531,7 @@
         <v>46144.34412430556</v>
       </c>
       <c r="D36" s="1">
-        <v>46144.59409722222</v>
+        <v>46144.34409722222</v>
       </c>
       <c r="E36">
         <v>54347</v>
@@ -41653,7 +41653,7 @@
         <v>46144.34429090278</v>
       </c>
       <c r="D37" s="1">
-        <v>46144.59427083333</v>
+        <v>46144.34427083333</v>
       </c>
       <c r="E37">
         <v>53792</v>
@@ -41796,7 +41796,7 @@
         <v>46144.3444721875</v>
       </c>
       <c r="D38" s="1">
-        <v>46144.59444444445</v>
+        <v>46144.34444444445</v>
       </c>
       <c r="E38">
         <v>53189</v>
@@ -41918,7 +41918,7 @@
         <v>46144.34463885416</v>
       </c>
       <c r="D39" s="1">
-        <v>46144.594618055555</v>
+        <v>46144.344618055555</v>
       </c>
       <c r="E39">
         <v>52646</v>
@@ -42061,7 +42061,7 @@
         <v>46144.34482320602</v>
       </c>
       <c r="D40" s="1">
-        <v>46144.59479166667</v>
+        <v>46144.34479166667</v>
       </c>
       <c r="E40">
         <v>52057</v>
@@ -42183,7 +42183,7 @@
         <v>46144.34498648148</v>
       </c>
       <c r="D41" s="1">
-        <v>46144.59496527778</v>
+        <v>46144.34496527778</v>
       </c>
       <c r="E41">
         <v>51533</v>
@@ -42326,7 +42326,7 @@
         <v>46144.34516600695</v>
       </c>
       <c r="D42" s="1">
-        <v>46144.595138888886</v>
+        <v>46144.345138888886</v>
       </c>
       <c r="E42">
         <v>50958</v>
@@ -42448,7 +42448,7 @@
         <v>46144.34533256944</v>
       </c>
       <c r="D43" s="1">
-        <v>46144.5953125</v>
+        <v>46144.3453125</v>
       </c>
       <c r="E43">
         <v>50455</v>
@@ -42591,7 +42591,7 @@
         <v>46144.34551351852</v>
       </c>
       <c r="D44" s="1">
-        <v>46144.59548611111</v>
+        <v>46144.34548611111</v>
       </c>
       <c r="E44">
         <v>49898</v>
@@ -42713,7 +42713,7 @@
         <v>46144.34567974537</v>
       </c>
       <c r="D45" s="1">
-        <v>46144.595659722225</v>
+        <v>46144.345659722225</v>
       </c>
       <c r="E45">
         <v>49407</v>
@@ -42856,7 +42856,7 @@
         <v>46144.34586396991</v>
       </c>
       <c r="D46" s="1">
-        <v>46144.59583333333</v>
+        <v>46144.34583333333</v>
       </c>
       <c r="E46">
         <v>48864</v>
@@ -42978,7 +42978,7 @@
         <v>46144.346027708336</v>
       </c>
       <c r="D47" s="1">
-        <v>46144.59600694444</v>
+        <v>46144.34600694444</v>
       </c>
       <c r="E47">
         <v>48390</v>
@@ -43121,7 +43121,7 @@
         <v>46144.346208599534</v>
       </c>
       <c r="D48" s="1">
-        <v>46144.596180555556</v>
+        <v>46144.346180555556</v>
       </c>
       <c r="E48">
         <v>47824</v>
@@ -43243,7 +43243,7 @@
         <v>46144.34637493055</v>
       </c>
       <c r="D49" s="1">
-        <v>46144.596354166664</v>
+        <v>46144.346354166664</v>
       </c>
       <c r="E49">
         <v>47304</v>
@@ -43386,7 +43386,7 @@
         <v>46144.34655504629</v>
       </c>
       <c r="D50" s="1">
-        <v>46144.59652777778</v>
+        <v>46144.34652777778</v>
       </c>
       <c r="E50">
         <v>46761</v>
@@ -43508,7 +43508,7 @@
         <v>46144.34672130787</v>
       </c>
       <c r="D51" s="1">
-        <v>46144.59670138889</v>
+        <v>46144.34670138889</v>
       </c>
       <c r="E51">
         <v>46285</v>
@@ -43651,7 +43651,7 @@
         <v>46144.34690585648</v>
       </c>
       <c r="D52" s="1">
-        <v>46144.596875</v>
+        <v>46144.346875</v>
       </c>
       <c r="E52">
         <v>45760</v>
@@ -43773,7 +43773,7 @@
         <v>46144.347069351854</v>
       </c>
       <c r="D53" s="1">
-        <v>46144.59704861111</v>
+        <v>46144.34704861111</v>
       </c>
       <c r="E53">
         <v>45303</v>
@@ -43916,7 +43916,7 @@
         <v>46144.347249108796</v>
       </c>
       <c r="D54" s="1">
-        <v>46144.59722222222</v>
+        <v>46144.34722222222</v>
       </c>
       <c r="E54">
         <v>44776</v>
@@ -44038,7 +44038,7 @@
         <v>46144.347597395834</v>
       </c>
       <c r="D55" s="1">
-        <v>46144.59756944444</v>
+        <v>46144.34756944444</v>
       </c>
       <c r="E55">
         <v>43824</v>
@@ -44160,7 +44160,7 @@
         <v>46144.347763541664</v>
       </c>
       <c r="D56" s="1">
-        <v>46144.59774305556</v>
+        <v>46144.34774305556</v>
       </c>
       <c r="E56">
         <v>43416</v>
@@ -44303,7 +44303,7 @@
         <v>46144.34794798611</v>
       </c>
       <c r="D57" s="1">
-        <v>46144.597916666666</v>
+        <v>46144.347916666666</v>
       </c>
       <c r="E57">
         <v>42935</v>
@@ -44425,7 +44425,7 @@
         <v>46144.348110844905</v>
       </c>
       <c r="D58" s="1">
-        <v>46144.59809027778</v>
+        <v>46144.34809027778</v>
       </c>
       <c r="E58">
         <v>42529</v>
@@ -44568,7 +44568,7 @@
         <v>46144.34829064815</v>
       </c>
       <c r="D59" s="1">
-        <v>46144.59826388889</v>
+        <v>46144.34826388889</v>
       </c>
       <c r="E59">
         <v>42072</v>
@@ -44690,7 +44690,7 @@
         <v>46144.34845773148</v>
       </c>
       <c r="D60" s="1">
-        <v>46144.5984375</v>
+        <v>46144.3484375</v>
       </c>
       <c r="E60">
         <v>41676</v>
@@ -44833,7 +44833,7 @@
         <v>46144.34863840278</v>
       </c>
       <c r="D61" s="1">
-        <v>46144.59861111111</v>
+        <v>46144.34861111111</v>
       </c>
       <c r="E61">
         <v>41219</v>
@@ -44955,7 +44955,7 @@
         <v>46144.34880454861</v>
       </c>
       <c r="D62" s="1">
-        <v>46144.59878472222</v>
+        <v>46144.34878472222</v>
       </c>
       <c r="E62">
         <v>40833</v>
@@ -45098,7 +45098,7 @@
         <v>46144.34899009259</v>
       </c>
       <c r="D63" s="1">
-        <v>46144.598958333336</v>
+        <v>46144.348958333336</v>
       </c>
       <c r="E63">
         <v>40379</v>
@@ -45220,7 +45220,7 @@
         <v>46144.349152766204</v>
       </c>
       <c r="D64" s="1">
-        <v>46144.599131944444</v>
+        <v>46144.349131944444</v>
       </c>
       <c r="E64">
         <v>39998</v>
@@ -45363,7 +45363,7 @@
         <v>46144.34949982639</v>
       </c>
       <c r="D65" s="1">
-        <v>46144.59947916667</v>
+        <v>46144.34947916667</v>
       </c>
       <c r="E65">
         <v>39200</v>
@@ -45506,7 +45506,7 @@
         <v>46144.34967960648</v>
       </c>
       <c r="D66" s="1">
-        <v>46144.599652777775</v>
+        <v>46144.349652777775</v>
       </c>
       <c r="E66">
         <v>38748</v>
@@ -45628,7 +45628,7 @@
         <v>46144.34984702546</v>
       </c>
       <c r="D67" s="1">
-        <v>46144.59982638889</v>
+        <v>46144.34982638889</v>
       </c>
       <c r="E67">
         <v>38401</v>
@@ -45771,7 +45771,7 @@
         <v>46144.35002644676</v>
       </c>
       <c r="D68" s="1">
-        <v>46144.6</v>
+        <v>46144.35</v>
       </c>
       <c r="E68">
         <v>37971</v>
@@ -45893,7 +45893,7 @@
         <v>46144.35019409722</v>
       </c>
       <c r="D69" s="1">
-        <v>46144.600173611114</v>
+        <v>46144.350173611114</v>
       </c>
       <c r="E69">
         <v>37643</v>
@@ -46036,7 +46036,7 @@
         <v>46144.35037822917</v>
       </c>
       <c r="D70" s="1">
-        <v>46144.60034722222</v>
+        <v>46144.35034722222</v>
       </c>
       <c r="E70">
         <v>37229</v>
@@ -46158,7 +46158,7 @@
         <v>46144.35054547454</v>
       </c>
       <c r="D71" s="1">
-        <v>46144.60052083333</v>
+        <v>46144.35052083333</v>
       </c>
       <c r="E71">
         <v>36903</v>
@@ -46301,7 +46301,7 @@
         <v>46144.35072190972</v>
       </c>
       <c r="D72" s="1">
-        <v>46144.600694444445</v>
+        <v>46144.350694444445</v>
       </c>
       <c r="E72">
         <v>36491</v>
@@ -46423,7 +46423,7 @@
         <v>46144.35088918982</v>
       </c>
       <c r="D73" s="1">
-        <v>46144.60086805555</v>
+        <v>46144.35086805555</v>
       </c>
       <c r="E73">
         <v>36177</v>
@@ -46566,7 +46566,7 @@
         <v>46144.351068668984</v>
       </c>
       <c r="D74" s="1">
-        <v>46144.60104166667</v>
+        <v>46144.35104166667</v>
       </c>
       <c r="E74">
         <v>35766</v>
@@ -46688,7 +46688,7 @@
         <v>46144.35123564815</v>
       </c>
       <c r="D75" s="1">
-        <v>46144.60121527778</v>
+        <v>46144.35121527778</v>
       </c>
       <c r="E75">
         <v>35450</v>
@@ -46831,7 +46831,7 @@
         <v>46144.35141981481</v>
       </c>
       <c r="D76" s="1">
-        <v>46144.60138888889</v>
+        <v>46144.35138888889</v>
       </c>
       <c r="E76">
         <v>35044</v>
@@ -46953,7 +46953,7 @@
         <v>46144.351583171294</v>
       </c>
       <c r="D77" s="1">
-        <v>46144.6015625</v>
+        <v>46144.3515625</v>
       </c>
       <c r="E77">
         <v>34720</v>
@@ -47096,7 +47096,7 @@
         <v>46144.351763113424</v>
       </c>
       <c r="D78" s="1">
-        <v>46144.60173611111</v>
+        <v>46144.35173611111</v>
       </c>
       <c r="E78">
         <v>34309</v>
@@ -47218,7 +47218,7 @@
         <v>46144.35193</v>
       </c>
       <c r="D79" s="1">
-        <v>46144.60190972222</v>
+        <v>46144.35190972222</v>
       </c>
       <c r="E79">
         <v>33995</v>
@@ -47361,7 +47361,7 @@
         <v>46144.35227792824</v>
       </c>
       <c r="D80" s="1">
-        <v>46144.60225694445</v>
+        <v>46144.35225694445</v>
       </c>
       <c r="E80">
         <v>33287</v>
@@ -47504,7 +47504,7 @@
         <v>46144.35246194444</v>
       </c>
       <c r="D81" s="1">
-        <v>46144.602430555555</v>
+        <v>46144.352430555555</v>
       </c>
       <c r="E81">
         <v>32875</v>
@@ -47626,7 +47626,7 @@
         <v>46144.35280361111</v>
       </c>
       <c r="D82" s="1">
-        <v>46144.60277777778</v>
+        <v>46144.35277777778</v>
       </c>
       <c r="E82">
         <v>32169</v>
@@ -47748,7 +47748,7 @@
         <v>46144.35297221065</v>
       </c>
       <c r="D83" s="1">
-        <v>46144.602951388886</v>
+        <v>46144.352951388886</v>
       </c>
       <c r="E83">
         <v>31864</v>
@@ -47891,7 +47891,7 @@
         <v>46144.35315070602</v>
       </c>
       <c r="D84" s="1">
-        <v>46144.603125</v>
+        <v>46144.353125</v>
       </c>
       <c r="E84">
         <v>31474</v>
@@ -48013,7 +48013,7 @@
         <v>46144.353319525464</v>
       </c>
       <c r="D85" s="1">
-        <v>46144.60329861111</v>
+        <v>46144.35329861111</v>
       </c>
       <c r="E85">
         <v>31165</v>
@@ -48156,7 +48156,7 @@
         <v>46144.353501770835</v>
       </c>
       <c r="D86" s="1">
-        <v>46144.603472222225</v>
+        <v>46144.353472222225</v>
       </c>
       <c r="E86">
         <v>30778</v>
@@ -48278,7 +48278,7 @@
         <v>46144.35366645833</v>
       </c>
       <c r="D87" s="1">
-        <v>46144.60364583333</v>
+        <v>46144.35364583333</v>
       </c>
       <c r="E87">
         <v>30477</v>
@@ -48421,7 +48421,7 @@
         <v>46144.35384510417</v>
       </c>
       <c r="D88" s="1">
-        <v>46144.60381944444</v>
+        <v>46144.35381944444</v>
       </c>
       <c r="E88">
         <v>30089</v>
@@ -48543,7 +48543,7 @@
         <v>46144.35401394676</v>
       </c>
       <c r="D89" s="1">
-        <v>46144.603993055556</v>
+        <v>46144.353993055556</v>
       </c>
       <c r="E89">
         <v>29787</v>
@@ -48686,7 +48686,7 @@
         <v>46144.35419222222</v>
       </c>
       <c r="D90" s="1">
-        <v>46144.604166666664</v>
+        <v>46144.354166666664</v>
       </c>
       <c r="E90">
         <v>29403</v>
@@ -48808,7 +48808,7 @@
         <v>46144.35436100695</v>
       </c>
       <c r="D91" s="1">
-        <v>46144.60434027778</v>
+        <v>46144.35434027778</v>
       </c>
       <c r="E91">
         <v>29102</v>
@@ -48951,7 +48951,7 @@
         <v>46144.354543506946</v>
       </c>
       <c r="D92" s="1">
-        <v>46144.60451388889</v>
+        <v>46144.35451388889</v>
       </c>
       <c r="E92">
         <v>28721</v>
@@ -49073,7 +49073,7 @@
         <v>46144.3547075</v>
       </c>
       <c r="D93" s="1">
-        <v>46144.6046875</v>
+        <v>46144.3546875</v>
       </c>
       <c r="E93">
         <v>28424</v>
@@ -49216,7 +49216,7 @@
         <v>46144.35488679398</v>
       </c>
       <c r="D94" s="1">
-        <v>46144.60486111111</v>
+        <v>46144.35486111111</v>
       </c>
       <c r="E94">
         <v>28038</v>
@@ -49338,7 +49338,7 @@
         <v>46144.35505532407</v>
       </c>
       <c r="D95" s="1">
-        <v>46144.60503472222</v>
+        <v>46144.35503472222</v>
       </c>
       <c r="E95">
         <v>27746</v>
@@ -49481,7 +49481,7 @@
         <v>46144.35523403935</v>
       </c>
       <c r="D96" s="1">
-        <v>46144.605208333334</v>
+        <v>46144.355208333334</v>
       </c>
       <c r="E96">
         <v>27356</v>
@@ -49603,7 +49603,7 @@
         <v>46144.35540255787</v>
       </c>
       <c r="D97" s="1">
-        <v>46144.60538194444</v>
+        <v>46144.35538194444</v>
       </c>
       <c r="E97">
         <v>27066</v>
@@ -49746,7 +49746,7 @@
         <v>46144.3555849537</v>
       </c>
       <c r="D98" s="1">
-        <v>46144.60555555556</v>
+        <v>46144.35555555556</v>
       </c>
       <c r="E98">
         <v>26677</v>
@@ -49868,7 +49868,7 @@
         <v>46144.355750358794</v>
       </c>
       <c r="D99" s="1">
-        <v>46144.605729166666</v>
+        <v>46144.355729166666</v>
       </c>
       <c r="E99">
         <v>26396</v>
@@ -50011,7 +50011,7 @@
         <v>46144.35592858796</v>
       </c>
       <c r="D100" s="1">
-        <v>46144.60590277778</v>
+        <v>46144.35590277778</v>
       </c>
       <c r="E100">
         <v>26017</v>
@@ -50133,7 +50133,7 @@
         <v>46144.35609623843</v>
       </c>
       <c r="D101" s="1">
-        <v>46144.60607638889</v>
+        <v>46144.35607638889</v>
       </c>
       <c r="E101">
         <v>25743</v>
@@ -50276,7 +50276,7 @@
         <v>46144.3562759375</v>
       </c>
       <c r="D102" s="1">
-        <v>46144.60625</v>
+        <v>46144.35625</v>
       </c>
       <c r="E102">
         <v>25371</v>
@@ -50398,7 +50398,7 @@
         <v>46144.35644380787</v>
       </c>
       <c r="D103" s="1">
-        <v>46144.60642361111</v>
+        <v>46144.35642361111</v>
       </c>
       <c r="E103">
         <v>25106</v>
@@ -50541,7 +50541,7 @@
         <v>46144.356626597226</v>
       </c>
       <c r="D104" s="1">
-        <v>46144.60659722222</v>
+        <v>46144.35659722222</v>
       </c>
       <c r="E104">
         <v>24737</v>
@@ -50663,7 +50663,7 @@
         <v>46144.356791481485</v>
       </c>
       <c r="D105" s="1">
-        <v>46144.606770833336</v>
+        <v>46144.356770833336</v>
       </c>
       <c r="E105">
         <v>24471</v>
@@ -50806,7 +50806,7 @@
         <v>46144.35697060185</v>
       </c>
       <c r="D106" s="1">
-        <v>46144.606944444444</v>
+        <v>46144.356944444444</v>
       </c>
       <c r="E106">
         <v>24114</v>
@@ -50928,7 +50928,7 @@
         <v>46144.357138657404</v>
       </c>
       <c r="D107" s="1">
-        <v>46144.60711805556</v>
+        <v>46144.35711805556</v>
       </c>
       <c r="E107">
         <v>23855</v>
@@ -51071,7 +51071,7 @@
         <v>46144.357318587965</v>
       </c>
       <c r="D108" s="1">
-        <v>46144.60729166667</v>
+        <v>46144.35729166667</v>
       </c>
       <c r="E108">
         <v>23497</v>
@@ -51193,7 +51193,7 @@
         <v>46144.35748643518</v>
       </c>
       <c r="D109" s="1">
-        <v>46144.607465277775</v>
+        <v>46144.357465277775</v>
       </c>
       <c r="E109">
         <v>23244</v>
@@ -51336,7 +51336,7 @@
         <v>46144.35766916667</v>
       </c>
       <c r="D110" s="1">
-        <v>46144.60763888889</v>
+        <v>46144.35763888889</v>
       </c>
       <c r="E110">
         <v>22890</v>
@@ -51458,7 +51458,7 @@
         <v>46144.357834490744</v>
       </c>
       <c r="D111" s="1">
-        <v>46144.6078125</v>
+        <v>46144.3578125</v>
       </c>
       <c r="E111">
         <v>22645</v>
@@ -51601,7 +51601,7 @@
         <v>46144.358013425925</v>
       </c>
       <c r="D112" s="1">
-        <v>46144.607986111114</v>
+        <v>46144.357986111114</v>
       </c>
       <c r="E112">
         <v>22303</v>
@@ -51723,7 +51723,7 @@
         <v>46144.35817988426</v>
       </c>
       <c r="D113" s="1">
-        <v>46144.60815972222</v>
+        <v>46144.35815972222</v>
       </c>
       <c r="E113">
         <v>22059</v>
@@ -51866,7 +51866,7 @@
         <v>46144.35836068287</v>
       </c>
       <c r="D114" s="1">
-        <v>46144.60833333333</v>
+        <v>46144.35833333333</v>
       </c>
       <c r="E114">
         <v>21719</v>
@@ -51988,7 +51988,7 @@
         <v>46144.358526828706</v>
       </c>
       <c r="D115" s="1">
-        <v>46144.608506944445</v>
+        <v>46144.358506944445</v>
       </c>
       <c r="E115">
         <v>21481</v>
@@ -52131,7 +52131,7 @@
         <v>46144.35871100694</v>
       </c>
       <c r="D116" s="1">
-        <v>46144.60868055555</v>
+        <v>46144.35868055555</v>
       </c>
       <c r="E116">
         <v>21141</v>
@@ -52253,7 +52253,7 @@
         <v>46144.35887467593</v>
       </c>
       <c r="D117" s="1">
-        <v>46144.60885416667</v>
+        <v>46144.35885416667</v>
       </c>
       <c r="E117">
         <v>20899</v>
@@ -52396,7 +52396,7 @@
         <v>46144.35905537037</v>
       </c>
       <c r="D118" s="1">
-        <v>46144.60902777778</v>
+        <v>46144.35902777778</v>
       </c>
       <c r="E118">
         <v>20560</v>
@@ -52518,7 +52518,7 @@
         <v>46144.359221203704</v>
       </c>
       <c r="D119" s="1">
-        <v>46144.60920138889</v>
+        <v>46144.35920138889</v>
       </c>
       <c r="E119">
         <v>20329</v>
@@ -52661,7 +52661,7 @@
         <v>46144.35940159722</v>
       </c>
       <c r="D120" s="1">
-        <v>46144.609375</v>
+        <v>46144.359375</v>
       </c>
       <c r="E120">
         <v>19996</v>
@@ -52783,7 +52783,7 @@
         <v>46144.35956916666</v>
       </c>
       <c r="D121" s="1">
-        <v>46144.60954861111</v>
+        <v>46144.35954861111</v>
       </c>
       <c r="E121">
         <v>19774</v>
@@ -52926,7 +52926,7 @@
         <v>46144.359753275465</v>
       </c>
       <c r="D122" s="1">
-        <v>46144.60972222222</v>
+        <v>46144.35972222222</v>
       </c>
       <c r="E122">
         <v>19445</v>
@@ -53048,7 +53048,7 @@
         <v>46144.35991719907</v>
       </c>
       <c r="D123" s="1">
-        <v>46144.60989583333</v>
+        <v>46144.35989583333</v>
       </c>
       <c r="E123">
         <v>19223</v>
@@ -53191,7 +53191,7 @@
         <v>46144.36009652778</v>
       </c>
       <c r="D124" s="1">
-        <v>46144.61006944445</v>
+        <v>46144.36006944445</v>
       </c>
       <c r="E124">
         <v>18893</v>
@@ -53313,7 +53313,7 @@
         <v>46144.36026553241</v>
       </c>
       <c r="D125" s="1">
-        <v>46144.610243055555</v>
+        <v>46144.360243055555</v>
       </c>
       <c r="E125">
         <v>18669</v>
@@ -53456,7 +53456,7 @@
         <v>46144.36044366898</v>
       </c>
       <c r="D126" s="1">
-        <v>46144.61041666667</v>
+        <v>46144.36041666667</v>
       </c>
       <c r="E126">
         <v>18342</v>
@@ -53578,7 +53578,7 @@
         <v>46144.36061083333</v>
       </c>
       <c r="D127" s="1">
-        <v>46144.61059027778</v>
+        <v>46144.36059027778</v>
       </c>
       <c r="E127">
         <v>18120</v>
@@ -53721,7 +53721,7 @@
         <v>46144.36079493056</v>
       </c>
       <c r="D128" s="1">
-        <v>46144.610763888886</v>
+        <v>46144.360763888886</v>
       </c>
       <c r="E128">
         <v>17801</v>
@@ -53843,7 +53843,7 @@
         <v>46144.36095822917</v>
       </c>
       <c r="D129" s="1">
-        <v>46144.6109375</v>
+        <v>46144.3609375</v>
       </c>
       <c r="E129">
         <v>17576</v>
@@ -53986,7 +53986,7 @@
         <v>46144.36113790509</v>
       </c>
       <c r="D130" s="1">
-        <v>46144.61111111111</v>
+        <v>46144.36111111111</v>
       </c>
       <c r="E130">
         <v>17253</v>
@@ -54108,7 +54108,7 @@
         <v>46144.36130539352</v>
       </c>
       <c r="D131" s="1">
-        <v>46144.611284722225</v>
+        <v>46144.361284722225</v>
       </c>
       <c r="E131">
         <v>17032</v>
@@ -54251,7 +54251,7 @@
         <v>46144.36148545139</v>
       </c>
       <c r="D132" s="1">
-        <v>46144.61145833333</v>
+        <v>46144.36145833333</v>
       </c>
       <c r="E132">
         <v>16715</v>
@@ -54373,7 +54373,7 @@
         <v>46144.36165909722</v>
       </c>
       <c r="D133" s="1">
-        <v>46144.61163194444</v>
+        <v>46144.36163194444</v>
       </c>
       <c r="E133">
         <v>16503</v>
@@ -54516,7 +54516,7 @@
         <v>46144.36183619213</v>
       </c>
       <c r="D134" s="1">
-        <v>46144.611805555556</v>
+        <v>46144.361805555556</v>
       </c>
       <c r="E134">
         <v>16183</v>
@@ -54638,7 +54638,7 @@
         <v>46144.36199946759</v>
       </c>
       <c r="D135" s="1">
-        <v>46144.611979166664</v>
+        <v>46144.361979166664</v>
       </c>
       <c r="E135">
         <v>15972</v>
@@ -54781,7 +54781,7 @@
         <v>46144.362347152775</v>
       </c>
       <c r="D136" s="1">
-        <v>46144.61232638889</v>
+        <v>46144.36232638889</v>
       </c>
       <c r="E136">
         <v>15443</v>
@@ -54924,7 +54924,7 @@
         <v>46144.36252746528</v>
       </c>
       <c r="D137" s="1">
-        <v>46144.6125</v>
+        <v>46144.3625</v>
       </c>
       <c r="E137">
         <v>15127</v>
@@ -55046,7 +55046,7 @@
         <v>46144.36269405093</v>
       </c>
       <c r="D138" s="1">
-        <v>46144.61267361111</v>
+        <v>46144.36267361111</v>
       </c>
       <c r="E138">
         <v>14913</v>
@@ -55189,7 +55189,7 @@
         <v>46144.3628744213</v>
       </c>
       <c r="D139" s="1">
-        <v>46144.61284722222</v>
+        <v>46144.36284722222</v>
       </c>
       <c r="E139">
         <v>14595</v>
@@ -55311,7 +55311,7 @@
         <v>46144.36304091435</v>
       </c>
       <c r="D140" s="1">
-        <v>46144.613020833334</v>
+        <v>46144.363020833334</v>
       </c>
       <c r="E140">
         <v>14384</v>
@@ -55454,7 +55454,7 @@
         <v>46144.36322516204</v>
       </c>
       <c r="D141" s="1">
-        <v>46144.61319444444</v>
+        <v>46144.36319444444</v>
       </c>
       <c r="E141">
         <v>14070</v>
@@ -55576,7 +55576,7 @@
         <v>46144.36364979167</v>
       </c>
       <c r="D142" s="1">
-        <v>46144.61336805556</v>
+        <v>46144.36336805556</v>
       </c>
       <c r="E142">
         <v>13858</v>
@@ -55719,7 +55719,7 @@
         <v>46144.36356871528</v>
       </c>
       <c r="D143" s="1">
-        <v>46144.613541666666</v>
+        <v>46144.363541666666</v>
       </c>
       <c r="E143">
         <v>13548</v>
@@ -55841,7 +55841,7 @@
         <v>46144.3637359375</v>
       </c>
       <c r="D144" s="1">
-        <v>46144.61371527778</v>
+        <v>46144.36371527778</v>
       </c>
       <c r="E144">
         <v>13347</v>
@@ -55984,7 +55984,7 @@
         <v>46144.36391599537</v>
       </c>
       <c r="D145" s="1">
-        <v>46144.61388888889</v>
+        <v>46144.36388888889</v>
       </c>
       <c r="E145">
         <v>13036</v>
@@ -56106,7 +56106,7 @@
         <v>46144.36408277778</v>
       </c>
       <c r="D146" s="1">
-        <v>46144.6140625</v>
+        <v>46144.3640625</v>
       </c>
       <c r="E146">
         <v>12835</v>
@@ -56249,7 +56249,7 @@
         <v>46144.36426695602</v>
       </c>
       <c r="D147" s="1">
-        <v>46144.61423611111</v>
+        <v>46144.36423611111</v>
       </c>
       <c r="E147">
         <v>12525</v>
@@ -56371,7 +56371,7 @@
         <v>46144.364609930555</v>
       </c>
       <c r="D148" s="1">
-        <v>46144.614583333336</v>
+        <v>46144.364583333336</v>
       </c>
       <c r="E148">
         <v>12023</v>
@@ -56493,7 +56493,7 @@
         <v>46144.36477770833</v>
       </c>
       <c r="D149" s="1">
-        <v>46144.614756944444</v>
+        <v>46144.364756944444</v>
       </c>
       <c r="E149">
         <v>11826</v>
@@ -56636,7 +56636,7 @@
         <v>46144.36495752315</v>
       </c>
       <c r="D150" s="1">
-        <v>46144.61493055556</v>
+        <v>46144.36493055556</v>
       </c>
       <c r="E150">
         <v>11530</v>
@@ -56758,7 +56758,7 @@
         <v>46144.365124317126</v>
       </c>
       <c r="D151" s="1">
-        <v>46144.61510416667</v>
+        <v>46144.36510416667</v>
       </c>
       <c r="E151">
         <v>11340</v>
@@ -56901,7 +56901,7 @@
         <v>46144.36530885417</v>
       </c>
       <c r="D152" s="1">
-        <v>46144.615277777775</v>
+        <v>46144.365277777775</v>
       </c>
       <c r="E152">
         <v>11045</v>
@@ -57023,7 +57023,7 @@
         <v>46144.3654721875</v>
       </c>
       <c r="D153" s="1">
-        <v>46144.61545138889</v>
+        <v>46144.36545138889</v>
       </c>
       <c r="E153">
         <v>10858</v>
@@ -57166,7 +57166,7 @@
         <v>46144.36565231482</v>
       </c>
       <c r="D154" s="1">
-        <v>46144.615625</v>
+        <v>46144.365625</v>
       </c>
       <c r="E154">
         <v>10566</v>
@@ -57288,7 +57288,7 @@
         <v>46144.365818645834</v>
       </c>
       <c r="D155" s="1">
-        <v>46144.615798611114</v>
+        <v>46144.365798611114</v>
       </c>
       <c r="E155">
         <v>10375</v>
@@ -57431,7 +57431,7 @@
         <v>46144.36600170139</v>
       </c>
       <c r="D156" s="1">
-        <v>46144.61597222222</v>
+        <v>46144.36597222222</v>
       </c>
       <c r="E156">
         <v>10077</v>
@@ -57553,7 +57553,7 @@
         <v>46144.36616603009</v>
       </c>
       <c r="D157" s="1">
-        <v>46144.61614583333</v>
+        <v>46144.36614583333</v>
       </c>
       <c r="E157">
         <v>9889</v>
@@ -57696,7 +57696,7 @@
         <v>46144.36635024306</v>
       </c>
       <c r="D158" s="1">
-        <v>46144.616319444445</v>
+        <v>46144.366319444445</v>
       </c>
       <c r="E158">
         <v>9598</v>
@@ -57818,7 +57818,7 @@
         <v>46144.36651270834</v>
       </c>
       <c r="D159" s="1">
-        <v>46144.61649305555</v>
+        <v>46144.36649305555</v>
       </c>
       <c r="E159">
         <v>9410</v>
@@ -57961,7 +57961,7 @@
         <v>46144.36669361111</v>
       </c>
       <c r="D160" s="1">
-        <v>46144.61666666667</v>
+        <v>46144.36666666667</v>
       </c>
       <c r="E160">
         <v>9122</v>
@@ -58083,7 +58083,7 @@
         <v>46144.36686070602</v>
       </c>
       <c r="D161" s="1">
-        <v>46144.61684027778</v>
+        <v>46144.36684027778</v>
       </c>
       <c r="E161">
         <v>8932</v>
@@ -58226,7 +58226,7 @@
         <v>46144.36704276621</v>
       </c>
       <c r="D162" s="1">
-        <v>46144.61701388889</v>
+        <v>46144.36701388889</v>
       </c>
       <c r="E162">
         <v>8636</v>
@@ -58348,7 +58348,7 @@
         <v>46144.36720807871</v>
       </c>
       <c r="D163" s="1">
-        <v>46144.6171875</v>
+        <v>46144.3671875</v>
       </c>
       <c r="E163">
         <v>8460</v>
@@ -58491,7 +58491,7 @@
         <v>46144.36739341435</v>
       </c>
       <c r="D164" s="1">
-        <v>46144.61736111111</v>
+        <v>46144.36736111111</v>
       </c>
       <c r="E164">
         <v>8177</v>
@@ -58613,7 +58613,7 @@
         <v>46144.36773537037</v>
       </c>
       <c r="D165" s="1">
-        <v>46144.61770833333</v>
+        <v>46144.36770833333</v>
       </c>
       <c r="E165">
         <v>7711</v>
@@ -58735,7 +58735,7 @@
         <v>46144.36790505787</v>
       </c>
       <c r="D166" s="1">
-        <v>46144.61788194445</v>
+        <v>46144.36788194445</v>
       </c>
       <c r="E166">
         <v>7525</v>
